--- a/CCVAE/training_metrics/training_metrics.xlsx
+++ b/CCVAE/training_metrics/training_metrics.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J228"/>
+  <dimension ref="A1:L228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,30 +442,40 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Train KL</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Train β-KL</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Train SupCon</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Val Loss</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Val Recon</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Val KL</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>Val β-KL</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Val SupCon</t>
         </is>
@@ -485,21 +495,27 @@
         <v>2.7788</v>
       </c>
       <c r="E2" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="F2" t="n">
         <v>0.0411</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>3.907</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>4.7271</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>1.7693</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
+        <v>92.8912</v>
+      </c>
+      <c r="K2" t="n">
         <v>0.0693</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>3.8513</v>
       </c>
     </row>
@@ -517,21 +533,27 @@
         <v>1.6062</v>
       </c>
       <c r="E3" t="n">
+        <v>63.35570469798657</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.0944</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>3.854</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>4.1691</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>1.1902</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
+        <v>79.3168</v>
+      </c>
+      <c r="K3" t="n">
         <v>0.1184</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>3.8141</v>
       </c>
     </row>
@@ -549,21 +571,27 @@
         <v>1.2736</v>
       </c>
       <c r="E4" t="n">
+        <v>62.00892857142858</v>
+      </c>
+      <c r="F4" t="n">
         <v>0.1389</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>3.8263</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>3.9892</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>0.9788</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
+        <v>71.3839</v>
+      </c>
+      <c r="K4" t="n">
         <v>0.1598</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>3.8008</v>
       </c>
     </row>
@@ -581,21 +609,27 @@
         <v>1.1311</v>
       </c>
       <c r="E5" t="n">
+        <v>59.33110367892976</v>
+      </c>
+      <c r="F5" t="n">
         <v>0.1774</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>3.8099</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>3.9176</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>0.8782</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
+        <v>65.79130000000001</v>
+      </c>
+      <c r="K5" t="n">
         <v>0.1964</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>3.7907</v>
       </c>
     </row>
@@ -613,21 +647,27 @@
         <v>1.0507</v>
       </c>
       <c r="E6" t="n">
+        <v>56.75603217158177</v>
+      </c>
+      <c r="F6" t="n">
         <v>0.2117</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>3.7996</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>3.897</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>0.8310999999999999</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
+        <v>60.4979</v>
+      </c>
+      <c r="K6" t="n">
         <v>0.2258</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>3.7868</v>
       </c>
     </row>
@@ -645,21 +685,27 @@
         <v>0.9956</v>
       </c>
       <c r="E7" t="n">
+        <v>54.04017857142858</v>
+      </c>
+      <c r="F7" t="n">
         <v>0.2421</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>3.7983</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>3.8818</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>0.7864</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
+        <v>57.8089</v>
+      </c>
+      <c r="K7" t="n">
         <v>0.2589</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>3.782</v>
       </c>
     </row>
@@ -677,21 +723,27 @@
         <v>0.9621</v>
       </c>
       <c r="E8" t="n">
+        <v>51.47227533460803</v>
+      </c>
+      <c r="F8" t="n">
         <v>0.2692</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>3.7881</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>3.8782</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>0.7616000000000001</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
+        <v>54.0494</v>
+      </c>
+      <c r="K8" t="n">
         <v>0.2824</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>3.779</v>
       </c>
     </row>
@@ -709,21 +761,27 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="E9" t="n">
+        <v>49.21273031825796</v>
+      </c>
+      <c r="F9" t="n">
         <v>0.2938</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>3.786</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>3.8852</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>0.7455000000000001</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
+        <v>51.5325</v>
+      </c>
+      <c r="K9" t="n">
         <v>0.3077</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>3.776</v>
       </c>
     </row>
@@ -741,21 +799,27 @@
         <v>0.9219000000000001</v>
       </c>
       <c r="E10" t="n">
+        <v>47.09821428571428</v>
+      </c>
+      <c r="F10" t="n">
         <v>0.3165</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>3.7836</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>3.9008</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>0.7408</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
+        <v>49.0168</v>
+      </c>
+      <c r="K10" t="n">
         <v>0.3293</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>3.7743</v>
       </c>
     </row>
@@ -773,21 +837,27 @@
         <v>0.9087</v>
       </c>
       <c r="E11" t="n">
+        <v>45.28150134048258</v>
+      </c>
+      <c r="F11" t="n">
         <v>0.3378</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>3.784</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>3.9119</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>0.7308</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
+        <v>47.0127</v>
+      </c>
+      <c r="K11" t="n">
         <v>0.3509</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>3.7736</v>
       </c>
     </row>
@@ -805,21 +875,27 @@
         <v>0.9003</v>
       </c>
       <c r="E12" t="n">
+        <v>43.5931790499391</v>
+      </c>
+      <c r="F12" t="n">
         <v>0.3579</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>3.7791</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>3.9259</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>0.7343</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
+        <v>44.185</v>
+      </c>
+      <c r="K12" t="n">
         <v>0.3628</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>3.7718</v>
       </c>
     </row>
@@ -837,21 +913,27 @@
         <v>0.8957000000000001</v>
       </c>
       <c r="E13" t="n">
+        <v>42.04241071428572</v>
+      </c>
+      <c r="F13" t="n">
         <v>0.3767</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>3.7797</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>3.9454</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>0.7325</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
+        <v>43.0409</v>
+      </c>
+      <c r="K13" t="n">
         <v>0.3855</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>3.7698</v>
       </c>
     </row>
@@ -869,21 +951,27 @@
         <v>0.8908</v>
       </c>
       <c r="E14" t="n">
+        <v>40.71134020618556</v>
+      </c>
+      <c r="F14" t="n">
         <v>0.3949</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>3.7775</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>3.962</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>0.734</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
+        <v>41.3226</v>
+      </c>
+      <c r="K14" t="n">
         <v>0.401</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>3.7693</v>
       </c>
     </row>
@@ -901,21 +989,27 @@
         <v>0.8898</v>
       </c>
       <c r="E15" t="n">
+        <v>39.49282296650718</v>
+      </c>
+      <c r="F15" t="n">
         <v>0.4127</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>3.7717</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>3.9818</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>0.7339</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
+        <v>40.3657</v>
+      </c>
+      <c r="K15" t="n">
         <v>0.4218</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>3.7681</v>
       </c>
     </row>
@@ -933,21 +1027,27 @@
         <v>0.8905</v>
       </c>
       <c r="E16" t="n">
+        <v>38.41964285714286</v>
+      </c>
+      <c r="F16" t="n">
         <v>0.4303</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>3.7762</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>4.0039</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>0.7429</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
+        <v>38.9782</v>
+      </c>
+      <c r="K16" t="n">
         <v>0.4364</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>3.7661</v>
       </c>
     </row>
@@ -965,21 +1065,27 @@
         <v>0.889</v>
       </c>
       <c r="E17" t="n">
+        <v>37.46231155778894</v>
+      </c>
+      <c r="F17" t="n">
         <v>0.4473</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>3.7722</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>4.0213</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>0.74</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
+        <v>38.2134</v>
+      </c>
+      <c r="K17" t="n">
         <v>0.4564</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>3.7665</v>
       </c>
     </row>
@@ -997,21 +1103,27 @@
         <v>0.8907</v>
       </c>
       <c r="E18" t="n">
+        <v>36.57210401891253</v>
+      </c>
+      <c r="F18" t="n">
         <v>0.4641</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>3.7698</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>4.0456</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>0.7497</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
+        <v>37.1118</v>
+      </c>
+      <c r="K18" t="n">
         <v>0.4709</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>3.7666</v>
       </c>
     </row>
@@ -1029,21 +1141,27 @@
         <v>0.8942</v>
       </c>
       <c r="E19" t="n">
+        <v>35.70684523809523</v>
+      </c>
+      <c r="F19" t="n">
         <v>0.4799</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>3.7676</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>4.0682</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>0.7571</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
+        <v>36.2623</v>
+      </c>
+      <c r="K19" t="n">
         <v>0.4872</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>3.7651</v>
       </c>
     </row>
@@ -1061,21 +1179,27 @@
         <v>0.8982</v>
       </c>
       <c r="E20" t="n">
+        <v>34.91537376586741</v>
+      </c>
+      <c r="F20" t="n">
         <v>0.4951</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>3.7696</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>4.0817</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>0.755</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
+        <v>35.5038</v>
+      </c>
+      <c r="K20" t="n">
         <v>0.5034999999999999</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>3.7642</v>
       </c>
     </row>
@@ -1093,21 +1217,27 @@
         <v>0.9028</v>
       </c>
       <c r="E21" t="n">
+        <v>34.125920964501</v>
+      </c>
+      <c r="F21" t="n">
         <v>0.5095</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>3.7708</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>4.1034</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>0.7684</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
+        <v>34.2965</v>
+      </c>
+      <c r="K21" t="n">
         <v>0.512</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>3.764</v>
       </c>
     </row>
@@ -1125,21 +1255,27 @@
         <v>0.9077</v>
       </c>
       <c r="E22" t="n">
+        <v>33.39923469387755</v>
+      </c>
+      <c r="F22" t="n">
         <v>0.5237000000000001</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>3.7725</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>4.1238</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>0.7679</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
+        <v>34.0143</v>
+      </c>
+      <c r="K22" t="n">
         <v>0.5332</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>3.7637</v>
       </c>
     </row>
@@ -1157,21 +1293,27 @@
         <v>0.9124</v>
       </c>
       <c r="E23" t="n">
+        <v>32.73447015834348</v>
+      </c>
+      <c r="F23" t="n">
         <v>0.5375</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>3.767</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>4.1471</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>0.7833</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
+        <v>32.9803</v>
+      </c>
+      <c r="K23" t="n">
         <v>0.5416</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>3.763</v>
       </c>
     </row>
@@ -1189,21 +1331,27 @@
         <v>0.9194</v>
       </c>
       <c r="E24" t="n">
+        <v>32.06755969714618</v>
+      </c>
+      <c r="F24" t="n">
         <v>0.5506</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>3.7671</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>4.1688</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>0.7884</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
+        <v>32.5399</v>
+      </c>
+      <c r="K24" t="n">
         <v>0.5587</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>3.7622</v>
       </c>
     </row>
@@ -1221,21 +1369,27 @@
         <v>0.9265</v>
       </c>
       <c r="E25" t="n">
+        <v>31.41741071428572</v>
+      </c>
+      <c r="F25" t="n">
         <v>0.5629999999999999</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>3.7681</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>4.1843</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>0.7989000000000001</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
+        <v>31.4609</v>
+      </c>
+      <c r="K25" t="n">
         <v>0.5636</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>3.7625</v>
       </c>
     </row>
@@ -1253,21 +1407,27 @@
         <v>0.9332</v>
       </c>
       <c r="E26" t="n">
+        <v>30.80385852090032</v>
+      </c>
+      <c r="F26" t="n">
         <v>0.5748</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>3.7613</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>4.2087</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>0.8077</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
+        <v>31.0412</v>
+      </c>
+      <c r="K26" t="n">
         <v>0.5793</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>3.7622</v>
       </c>
     </row>
@@ -1285,21 +1445,27 @@
         <v>0.9406</v>
       </c>
       <c r="E27" t="n">
+        <v>30.1854714064915</v>
+      </c>
+      <c r="F27" t="n">
         <v>0.5859</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>3.7654</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>4.2304</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>0.8147</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
+        <v>30.6624</v>
+      </c>
+      <c r="K27" t="n">
         <v>0.5951</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>3.7607</v>
       </c>
     </row>
@@ -1317,21 +1483,27 @@
         <v>0.9475</v>
       </c>
       <c r="E28" t="n">
+        <v>29.61290322580645</v>
+      </c>
+      <c r="F28" t="n">
         <v>0.5967</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>3.7674</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>4.2465</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>0.8269</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
+        <v>29.7376</v>
+      </c>
+      <c r="K28" t="n">
         <v>0.5994</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>3.7603</v>
       </c>
     </row>
@@ -1349,21 +1521,27 @@
         <v>0.9547</v>
       </c>
       <c r="E29" t="n">
+        <v>29.04306220095694</v>
+      </c>
+      <c r="F29" t="n">
         <v>0.607</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>3.7685</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>4.2678</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>0.8352000000000001</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
+        <v>29.2671</v>
+      </c>
+      <c r="K29" t="n">
         <v>0.6117</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>3.7612</v>
       </c>
     </row>
@@ -1381,21 +1559,27 @@
         <v>0.9663</v>
       </c>
       <c r="E30" t="n">
+        <v>28.47575057736721</v>
+      </c>
+      <c r="F30" t="n">
         <v>0.6165</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>3.76</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>4.2864</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>0.843</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
+        <v>28.7703</v>
+      </c>
+      <c r="K30" t="n">
         <v>0.6228</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>3.7607</v>
       </c>
     </row>
@@ -1413,21 +1597,27 @@
         <v>0.976</v>
       </c>
       <c r="E31" t="n">
+        <v>27.90978115230013</v>
+      </c>
+      <c r="F31" t="n">
         <v>0.6249</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>3.7659</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>4.3061</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>0.8562</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
+        <v>28.1185</v>
+      </c>
+      <c r="K31" t="n">
         <v>0.6297</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>3.7602</v>
       </c>
     </row>
@@ -1445,21 +1635,27 @@
         <v>0.9839</v>
       </c>
       <c r="E32" t="n">
+        <v>27.38115816767502</v>
+      </c>
+      <c r="F32" t="n">
         <v>0.6336000000000001</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>3.7659</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>4.3239</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>0.8683</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
+        <v>27.473</v>
+      </c>
+      <c r="K32" t="n">
         <v>0.6357</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>3.7599</v>
       </c>
     </row>
@@ -1477,21 +1673,27 @@
         <v>0.9936</v>
       </c>
       <c r="E33" t="n">
+        <v>26.83549602344077</v>
+      </c>
+      <c r="F33" t="n">
         <v>0.6411</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>3.7639</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>4.3431</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>0.8779</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
+        <v>26.9959</v>
+      </c>
+      <c r="K33" t="n">
         <v>0.6449</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>3.7604</v>
       </c>
     </row>
@@ -1509,21 +1711,27 @@
         <v>1.003</v>
       </c>
       <c r="E34" t="n">
+        <v>26.32967925294356</v>
+      </c>
+      <c r="F34" t="n">
         <v>0.6485</v>
       </c>
-      <c r="F34" t="n">
+      <c r="G34" t="n">
         <v>3.7656</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>4.3616</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>0.8935999999999999</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
+        <v>26.3012</v>
+      </c>
+      <c r="K34" t="n">
         <v>0.6479</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>3.7601</v>
       </c>
     </row>
@@ -1541,21 +1749,27 @@
         <v>1.0123</v>
       </c>
       <c r="E35" t="n">
+        <v>26.144</v>
+      </c>
+      <c r="F35" t="n">
         <v>0.6536</v>
       </c>
-      <c r="F35" t="n">
+      <c r="G35" t="n">
         <v>3.7606</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>4.3695</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>0.8935</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
+        <v>26.2618</v>
+      </c>
+      <c r="K35" t="n">
         <v>0.6565</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>3.7591</v>
       </c>
     </row>
@@ -1573,21 +1787,27 @@
         <v>1.0121</v>
       </c>
       <c r="E36" t="n">
+        <v>26.12</v>
+      </c>
+      <c r="F36" t="n">
         <v>0.653</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>3.7664</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>4.3669</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>0.8875</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
+        <v>26.3855</v>
+      </c>
+      <c r="K36" t="n">
         <v>0.6596</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>3.7597</v>
       </c>
     </row>
@@ -1605,21 +1825,27 @@
         <v>1.0102</v>
       </c>
       <c r="E37" t="n">
+        <v>26.112</v>
+      </c>
+      <c r="F37" t="n">
         <v>0.6528</v>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>3.7633</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>4.3649</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>0.8957000000000001</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
+        <v>26.0091</v>
+      </c>
+      <c r="K37" t="n">
         <v>0.6502</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>3.7587</v>
       </c>
     </row>
@@ -1637,21 +1863,27 @@
         <v>1.0093</v>
       </c>
       <c r="E38" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="F38" t="n">
         <v>0.652</v>
       </c>
-      <c r="F38" t="n">
+      <c r="G38" t="n">
         <v>3.7616</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>4.3645</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>0.895</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
+        <v>26.0058</v>
+      </c>
+      <c r="K38" t="n">
         <v>0.6501</v>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
         <v>3.7591</v>
       </c>
     </row>
@@ -1669,21 +1901,27 @@
         <v>1.0072</v>
       </c>
       <c r="E39" t="n">
+        <v>26.084</v>
+      </c>
+      <c r="F39" t="n">
         <v>0.6521</v>
       </c>
-      <c r="F39" t="n">
+      <c r="G39" t="n">
         <v>3.7615</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>4.3608</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>0.8922</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
+        <v>25.9924</v>
+      </c>
+      <c r="K39" t="n">
         <v>0.6498</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>3.7584</v>
       </c>
     </row>
@@ -1701,21 +1939,27 @@
         <v>1.0053</v>
       </c>
       <c r="E40" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="F40" t="n">
         <v>0.652</v>
       </c>
-      <c r="F40" t="n">
+      <c r="G40" t="n">
         <v>3.7606</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>4.3627</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>0.8905</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
+        <v>26.1535</v>
+      </c>
+      <c r="K40" t="n">
         <v>0.6538</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>3.7578</v>
       </c>
     </row>
@@ -1733,21 +1977,27 @@
         <v>1.0027</v>
       </c>
       <c r="E41" t="n">
+        <v>26.072</v>
+      </c>
+      <c r="F41" t="n">
         <v>0.6518</v>
       </c>
-      <c r="F41" t="n">
+      <c r="G41" t="n">
         <v>3.761</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>4.3565</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>0.883</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
+        <v>26.19</v>
+      </c>
+      <c r="K41" t="n">
         <v>0.6546999999999999</v>
       </c>
-      <c r="J41" t="n">
+      <c r="L41" t="n">
         <v>3.7584</v>
       </c>
     </row>
@@ -1765,21 +2015,27 @@
         <v>1.0003</v>
       </c>
       <c r="E42" t="n">
+        <v>26.096</v>
+      </c>
+      <c r="F42" t="n">
         <v>0.6524</v>
       </c>
-      <c r="F42" t="n">
+      <c r="G42" t="n">
         <v>3.765</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>4.3547</v>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>0.8816000000000001</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
+        <v>26.1741</v>
+      </c>
+      <c r="K42" t="n">
         <v>0.6544</v>
       </c>
-      <c r="J42" t="n">
+      <c r="L42" t="n">
         <v>3.7584</v>
       </c>
     </row>
@@ -1797,21 +2053,27 @@
         <v>0.9986</v>
       </c>
       <c r="E43" t="n">
+        <v>26.096</v>
+      </c>
+      <c r="F43" t="n">
         <v>0.6524</v>
       </c>
-      <c r="F43" t="n">
+      <c r="G43" t="n">
         <v>3.757</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>4.3536</v>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>0.8882</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
+        <v>25.8847</v>
+      </c>
+      <c r="K43" t="n">
         <v>0.6471</v>
       </c>
-      <c r="J43" t="n">
+      <c r="L43" t="n">
         <v>3.7576</v>
       </c>
     </row>
@@ -1829,21 +2091,27 @@
         <v>0.9952</v>
       </c>
       <c r="E44" t="n">
+        <v>26.092</v>
+      </c>
+      <c r="F44" t="n">
         <v>0.6523</v>
       </c>
-      <c r="F44" t="n">
+      <c r="G44" t="n">
         <v>3.7604</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>4.3566</v>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>0.8872</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
+        <v>26.0625</v>
+      </c>
+      <c r="K44" t="n">
         <v>0.6516</v>
       </c>
-      <c r="J44" t="n">
+      <c r="L44" t="n">
         <v>3.7571</v>
       </c>
     </row>
@@ -1861,21 +2129,27 @@
         <v>0.9946</v>
       </c>
       <c r="E45" t="n">
+        <v>26.116</v>
+      </c>
+      <c r="F45" t="n">
         <v>0.6529</v>
       </c>
-      <c r="F45" t="n">
+      <c r="G45" t="n">
         <v>3.7623</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>4.3486</v>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>0.8841</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
+        <v>25.8585</v>
+      </c>
+      <c r="K45" t="n">
         <v>0.6465</v>
       </c>
-      <c r="J45" t="n">
+      <c r="L45" t="n">
         <v>3.7574</v>
       </c>
     </row>
@@ -1893,21 +2167,27 @@
         <v>0.9912</v>
       </c>
       <c r="E46" t="n">
+        <v>26.108</v>
+      </c>
+      <c r="F46" t="n">
         <v>0.6526999999999999</v>
       </c>
-      <c r="F46" t="n">
+      <c r="G46" t="n">
         <v>3.7617</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>4.3488</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>0.8815</v>
       </c>
-      <c r="I46" t="n">
+      <c r="J46" t="n">
+        <v>25.9751</v>
+      </c>
+      <c r="K46" t="n">
         <v>0.6494</v>
       </c>
-      <c r="J46" t="n">
+      <c r="L46" t="n">
         <v>3.7572</v>
       </c>
     </row>
@@ -1925,21 +2205,27 @@
         <v>0.9893</v>
       </c>
       <c r="E47" t="n">
+        <v>26.124</v>
+      </c>
+      <c r="F47" t="n">
         <v>0.6531</v>
       </c>
-      <c r="F47" t="n">
+      <c r="G47" t="n">
         <v>3.7617</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>4.3512</v>
       </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>0.8861</v>
       </c>
-      <c r="I47" t="n">
+      <c r="J47" t="n">
+        <v>25.861</v>
+      </c>
+      <c r="K47" t="n">
         <v>0.6465</v>
       </c>
-      <c r="J47" t="n">
+      <c r="L47" t="n">
         <v>3.7581</v>
       </c>
     </row>
@@ -1957,21 +2243,27 @@
         <v>0.9866</v>
       </c>
       <c r="E48" t="n">
+        <v>26.152</v>
+      </c>
+      <c r="F48" t="n">
         <v>0.6538</v>
       </c>
-      <c r="F48" t="n">
+      <c r="G48" t="n">
         <v>3.7563</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>4.3466</v>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>0.8731</v>
       </c>
-      <c r="I48" t="n">
+      <c r="J48" t="n">
+        <v>26.2319</v>
+      </c>
+      <c r="K48" t="n">
         <v>0.6558</v>
       </c>
-      <c r="J48" t="n">
+      <c r="L48" t="n">
         <v>3.7569</v>
       </c>
     </row>
@@ -1989,21 +2281,27 @@
         <v>0.9855</v>
       </c>
       <c r="E49" t="n">
+        <v>26.156</v>
+      </c>
+      <c r="F49" t="n">
         <v>0.6539</v>
       </c>
-      <c r="F49" t="n">
+      <c r="G49" t="n">
         <v>3.762</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>4.3448</v>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>0.8686</v>
       </c>
-      <c r="I49" t="n">
+      <c r="J49" t="n">
+        <v>26.3319</v>
+      </c>
+      <c r="K49" t="n">
         <v>0.6583</v>
       </c>
-      <c r="J49" t="n">
+      <c r="L49" t="n">
         <v>3.7571</v>
       </c>
     </row>
@@ -2021,21 +2319,27 @@
         <v>0.9833</v>
       </c>
       <c r="E50" t="n">
+        <v>26.172</v>
+      </c>
+      <c r="F50" t="n">
         <v>0.6543</v>
       </c>
-      <c r="F50" t="n">
+      <c r="G50" t="n">
         <v>3.7585</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>4.344</v>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>0.8665</v>
       </c>
-      <c r="I50" t="n">
+      <c r="J50" t="n">
+        <v>26.3989</v>
+      </c>
+      <c r="K50" t="n">
         <v>0.66</v>
       </c>
-      <c r="J50" t="n">
+      <c r="L50" t="n">
         <v>3.7568</v>
       </c>
     </row>
@@ -2053,21 +2357,27 @@
         <v>0.9818</v>
       </c>
       <c r="E51" t="n">
+        <v>26.188</v>
+      </c>
+      <c r="F51" t="n">
         <v>0.6546999999999999</v>
       </c>
-      <c r="F51" t="n">
+      <c r="G51" t="n">
         <v>3.7573</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>4.34</v>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>0.8643999999999999</v>
       </c>
-      <c r="I51" t="n">
+      <c r="J51" t="n">
+        <v>26.3344</v>
+      </c>
+      <c r="K51" t="n">
         <v>0.6584</v>
       </c>
-      <c r="J51" t="n">
+      <c r="L51" t="n">
         <v>3.7564</v>
       </c>
     </row>
@@ -2085,21 +2395,27 @@
         <v>0.9798</v>
       </c>
       <c r="E52" t="n">
+        <v>26.204</v>
+      </c>
+      <c r="F52" t="n">
         <v>0.6551</v>
       </c>
-      <c r="F52" t="n">
+      <c r="G52" t="n">
         <v>3.7599</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>4.34</v>
       </c>
-      <c r="H52" t="n">
+      <c r="I52" t="n">
         <v>0.865</v>
       </c>
-      <c r="I52" t="n">
+      <c r="J52" t="n">
+        <v>26.3034</v>
+      </c>
+      <c r="K52" t="n">
         <v>0.6576</v>
       </c>
-      <c r="J52" t="n">
+      <c r="L52" t="n">
         <v>3.7565</v>
       </c>
     </row>
@@ -2117,21 +2433,27 @@
         <v>0.977</v>
       </c>
       <c r="E53" t="n">
+        <v>26.224</v>
+      </c>
+      <c r="F53" t="n">
         <v>0.6556</v>
       </c>
-      <c r="F53" t="n">
+      <c r="G53" t="n">
         <v>3.7605</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>4.339</v>
       </c>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
         <v>0.8657</v>
       </c>
-      <c r="I53" t="n">
+      <c r="J53" t="n">
+        <v>26.232</v>
+      </c>
+      <c r="K53" t="n">
         <v>0.6558</v>
       </c>
-      <c r="J53" t="n">
+      <c r="L53" t="n">
         <v>3.7567</v>
       </c>
     </row>
@@ -2149,21 +2471,27 @@
         <v>0.9752</v>
       </c>
       <c r="E54" t="n">
+        <v>26.236</v>
+      </c>
+      <c r="F54" t="n">
         <v>0.6559</v>
       </c>
-      <c r="F54" t="n">
+      <c r="G54" t="n">
         <v>3.7615</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>4.3382</v>
       </c>
-      <c r="H54" t="n">
+      <c r="I54" t="n">
         <v>0.8672</v>
       </c>
-      <c r="I54" t="n">
+      <c r="J54" t="n">
+        <v>26.1493</v>
+      </c>
+      <c r="K54" t="n">
         <v>0.6536999999999999</v>
       </c>
-      <c r="J54" t="n">
+      <c r="L54" t="n">
         <v>3.7564</v>
       </c>
     </row>
@@ -2181,21 +2509,27 @@
         <v>0.9747</v>
       </c>
       <c r="E55" t="n">
+        <v>26.244</v>
+      </c>
+      <c r="F55" t="n">
         <v>0.6561</v>
       </c>
-      <c r="F55" t="n">
+      <c r="G55" t="n">
         <v>3.7595</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>4.3404</v>
       </c>
-      <c r="H55" t="n">
+      <c r="I55" t="n">
         <v>0.8607</v>
       </c>
-      <c r="I55" t="n">
+      <c r="J55" t="n">
+        <v>26.5111</v>
+      </c>
+      <c r="K55" t="n">
         <v>0.6627999999999999</v>
       </c>
-      <c r="J55" t="n">
+      <c r="L55" t="n">
         <v>3.7558</v>
       </c>
     </row>
@@ -2213,21 +2547,27 @@
         <v>0.9705</v>
       </c>
       <c r="E56" t="n">
+        <v>26.28</v>
+      </c>
+      <c r="F56" t="n">
         <v>0.657</v>
       </c>
-      <c r="F56" t="n">
+      <c r="G56" t="n">
         <v>3.7612</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>4.334</v>
       </c>
-      <c r="H56" t="n">
+      <c r="I56" t="n">
         <v>0.8605</v>
       </c>
-      <c r="I56" t="n">
+      <c r="J56" t="n">
+        <v>26.2572</v>
+      </c>
+      <c r="K56" t="n">
         <v>0.6564</v>
       </c>
-      <c r="J56" t="n">
+      <c r="L56" t="n">
         <v>3.756</v>
       </c>
     </row>
@@ -2245,21 +2585,27 @@
         <v>0.971</v>
       </c>
       <c r="E57" t="n">
+        <v>26.288</v>
+      </c>
+      <c r="F57" t="n">
         <v>0.6572</v>
       </c>
-      <c r="F57" t="n">
+      <c r="G57" t="n">
         <v>3.7554</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>4.3329</v>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>0.8624000000000001</v>
       </c>
-      <c r="I57" t="n">
+      <c r="J57" t="n">
+        <v>26.1494</v>
+      </c>
+      <c r="K57" t="n">
         <v>0.6536999999999999</v>
       </c>
-      <c r="J57" t="n">
+      <c r="L57" t="n">
         <v>3.7556</v>
       </c>
     </row>
@@ -2277,21 +2623,27 @@
         <v>0.9671</v>
       </c>
       <c r="E58" t="n">
+        <v>26.308</v>
+      </c>
+      <c r="F58" t="n">
         <v>0.6577</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>3.7603</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>4.3318</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>0.8596</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
+        <v>26.2111</v>
+      </c>
+      <c r="K58" t="n">
         <v>0.6553</v>
       </c>
-      <c r="J58" t="n">
+      <c r="L58" t="n">
         <v>3.7559</v>
       </c>
     </row>
@@ -2309,21 +2661,27 @@
         <v>0.9661999999999999</v>
       </c>
       <c r="E59" t="n">
+        <v>26.324</v>
+      </c>
+      <c r="F59" t="n">
         <v>0.6581</v>
       </c>
-      <c r="F59" t="n">
+      <c r="G59" t="n">
         <v>3.759</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>4.3302</v>
       </c>
-      <c r="H59" t="n">
+      <c r="I59" t="n">
         <v>0.8546</v>
       </c>
-      <c r="I59" t="n">
+      <c r="J59" t="n">
+        <v>26.365</v>
+      </c>
+      <c r="K59" t="n">
         <v>0.6591</v>
       </c>
-      <c r="J59" t="n">
+      <c r="L59" t="n">
         <v>3.7553</v>
       </c>
     </row>
@@ -2341,21 +2699,27 @@
         <v>0.9641</v>
       </c>
       <c r="E60" t="n">
+        <v>26.356</v>
+      </c>
+      <c r="F60" t="n">
         <v>0.6589</v>
       </c>
-      <c r="F60" t="n">
+      <c r="G60" t="n">
         <v>3.7587</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>4.3352</v>
       </c>
-      <c r="H60" t="n">
+      <c r="I60" t="n">
         <v>0.8615</v>
       </c>
-      <c r="I60" t="n">
+      <c r="J60" t="n">
+        <v>26.299</v>
+      </c>
+      <c r="K60" t="n">
         <v>0.6575</v>
       </c>
-      <c r="J60" t="n">
+      <c r="L60" t="n">
         <v>3.7551</v>
       </c>
     </row>
@@ -2373,21 +2737,27 @@
         <v>0.9641</v>
       </c>
       <c r="E61" t="n">
+        <v>26.348</v>
+      </c>
+      <c r="F61" t="n">
         <v>0.6587</v>
       </c>
-      <c r="F61" t="n">
+      <c r="G61" t="n">
         <v>3.759</v>
       </c>
-      <c r="G61" t="n">
+      <c r="H61" t="n">
         <v>4.3288</v>
       </c>
-      <c r="H61" t="n">
+      <c r="I61" t="n">
         <v>0.8552</v>
       </c>
-      <c r="I61" t="n">
+      <c r="J61" t="n">
+        <v>26.2749</v>
+      </c>
+      <c r="K61" t="n">
         <v>0.6569</v>
       </c>
-      <c r="J61" t="n">
+      <c r="L61" t="n">
         <v>3.7557</v>
       </c>
     </row>
@@ -2405,21 +2775,27 @@
         <v>0.9617</v>
       </c>
       <c r="E62" t="n">
+        <v>26.364</v>
+      </c>
+      <c r="F62" t="n">
         <v>0.6591</v>
       </c>
-      <c r="F62" t="n">
+      <c r="G62" t="n">
         <v>3.7571</v>
       </c>
-      <c r="G62" t="n">
+      <c r="H62" t="n">
         <v>4.3289</v>
       </c>
-      <c r="H62" t="n">
+      <c r="I62" t="n">
         <v>0.8499</v>
       </c>
-      <c r="I62" t="n">
+      <c r="J62" t="n">
+        <v>26.4875</v>
+      </c>
+      <c r="K62" t="n">
         <v>0.6622</v>
       </c>
-      <c r="J62" t="n">
+      <c r="L62" t="n">
         <v>3.7558</v>
       </c>
     </row>
@@ -2437,21 +2813,27 @@
         <v>0.9592000000000001</v>
       </c>
       <c r="E63" t="n">
+        <v>26.38</v>
+      </c>
+      <c r="F63" t="n">
         <v>0.6595</v>
       </c>
-      <c r="F63" t="n">
+      <c r="G63" t="n">
         <v>3.7616</v>
       </c>
-      <c r="G63" t="n">
+      <c r="H63" t="n">
         <v>4.3277</v>
       </c>
-      <c r="H63" t="n">
+      <c r="I63" t="n">
         <v>0.854</v>
       </c>
-      <c r="I63" t="n">
+      <c r="J63" t="n">
+        <v>26.2886</v>
+      </c>
+      <c r="K63" t="n">
         <v>0.6572</v>
       </c>
-      <c r="J63" t="n">
+      <c r="L63" t="n">
         <v>3.7554</v>
       </c>
     </row>
@@ -2469,21 +2851,27 @@
         <v>0.9568</v>
       </c>
       <c r="E64" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="F64" t="n">
         <v>0.6605</v>
       </c>
-      <c r="F64" t="n">
+      <c r="G64" t="n">
         <v>3.7562</v>
       </c>
-      <c r="G64" t="n">
+      <c r="H64" t="n">
         <v>4.3254</v>
       </c>
-      <c r="H64" t="n">
+      <c r="I64" t="n">
         <v>0.8467</v>
       </c>
-      <c r="I64" t="n">
+      <c r="J64" t="n">
+        <v>26.5122</v>
+      </c>
+      <c r="K64" t="n">
         <v>0.6627999999999999</v>
       </c>
-      <c r="J64" t="n">
+      <c r="L64" t="n">
         <v>3.7546</v>
       </c>
     </row>
@@ -2501,21 +2889,27 @@
         <v>0.9557</v>
       </c>
       <c r="E65" t="n">
+        <v>26.436</v>
+      </c>
+      <c r="F65" t="n">
         <v>0.6609</v>
       </c>
-      <c r="F65" t="n">
+      <c r="G65" t="n">
         <v>3.7561</v>
       </c>
-      <c r="G65" t="n">
+      <c r="H65" t="n">
         <v>4.3259</v>
       </c>
-      <c r="H65" t="n">
+      <c r="I65" t="n">
         <v>0.8489</v>
       </c>
-      <c r="I65" t="n">
+      <c r="J65" t="n">
+        <v>26.4578</v>
+      </c>
+      <c r="K65" t="n">
         <v>0.6614</v>
       </c>
-      <c r="J65" t="n">
+      <c r="L65" t="n">
         <v>3.7541</v>
       </c>
     </row>
@@ -2533,21 +2927,27 @@
         <v>0.9548</v>
       </c>
       <c r="E66" t="n">
+        <v>26.432</v>
+      </c>
+      <c r="F66" t="n">
         <v>0.6608000000000001</v>
       </c>
-      <c r="F66" t="n">
+      <c r="G66" t="n">
         <v>3.7589</v>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>4.3222</v>
       </c>
-      <c r="H66" t="n">
+      <c r="I66" t="n">
         <v>0.8428</v>
       </c>
-      <c r="I66" t="n">
+      <c r="J66" t="n">
+        <v>26.5158</v>
+      </c>
+      <c r="K66" t="n">
         <v>0.6629</v>
       </c>
-      <c r="J66" t="n">
+      <c r="L66" t="n">
         <v>3.7554</v>
       </c>
     </row>
@@ -2565,21 +2965,27 @@
         <v>0.9532</v>
       </c>
       <c r="E67" t="n">
+        <v>26.456</v>
+      </c>
+      <c r="F67" t="n">
         <v>0.6614</v>
       </c>
-      <c r="F67" t="n">
+      <c r="G67" t="n">
         <v>3.7583</v>
       </c>
-      <c r="G67" t="n">
+      <c r="H67" t="n">
         <v>4.3232</v>
       </c>
-      <c r="H67" t="n">
+      <c r="I67" t="n">
         <v>0.8455</v>
       </c>
-      <c r="I67" t="n">
+      <c r="J67" t="n">
+        <v>26.455</v>
+      </c>
+      <c r="K67" t="n">
         <v>0.6614</v>
       </c>
-      <c r="J67" t="n">
+      <c r="L67" t="n">
         <v>3.7552</v>
       </c>
     </row>
@@ -2597,21 +3003,27 @@
         <v>0.9512</v>
       </c>
       <c r="E68" t="n">
+        <v>26.472</v>
+      </c>
+      <c r="F68" t="n">
         <v>0.6618000000000001</v>
       </c>
-      <c r="F68" t="n">
+      <c r="G68" t="n">
         <v>3.7587</v>
       </c>
-      <c r="G68" t="n">
+      <c r="H68" t="n">
         <v>4.3222</v>
       </c>
-      <c r="H68" t="n">
+      <c r="I68" t="n">
         <v>0.8471</v>
       </c>
-      <c r="I68" t="n">
+      <c r="J68" t="n">
+        <v>26.3505</v>
+      </c>
+      <c r="K68" t="n">
         <v>0.6588000000000001</v>
       </c>
-      <c r="J68" t="n">
+      <c r="L68" t="n">
         <v>3.7551</v>
       </c>
     </row>
@@ -2629,21 +3041,27 @@
         <v>0.9507</v>
       </c>
       <c r="E69" t="n">
+        <v>26.48</v>
+      </c>
+      <c r="F69" t="n">
         <v>0.662</v>
       </c>
-      <c r="F69" t="n">
+      <c r="G69" t="n">
         <v>3.7599</v>
       </c>
-      <c r="G69" t="n">
+      <c r="H69" t="n">
         <v>4.3181</v>
       </c>
-      <c r="H69" t="n">
+      <c r="I69" t="n">
         <v>0.8408</v>
       </c>
-      <c r="I69" t="n">
+      <c r="J69" t="n">
+        <v>26.4567</v>
+      </c>
+      <c r="K69" t="n">
         <v>0.6614</v>
       </c>
-      <c r="J69" t="n">
+      <c r="L69" t="n">
         <v>3.7545</v>
       </c>
     </row>
@@ -2661,21 +3079,27 @@
         <v>0.9483</v>
       </c>
       <c r="E70" t="n">
+        <v>26.492</v>
+      </c>
+      <c r="F70" t="n">
         <v>0.6623</v>
       </c>
-      <c r="F70" t="n">
+      <c r="G70" t="n">
         <v>3.7556</v>
       </c>
-      <c r="G70" t="n">
+      <c r="H70" t="n">
         <v>4.321</v>
       </c>
-      <c r="H70" t="n">
+      <c r="I70" t="n">
         <v>0.842</v>
       </c>
-      <c r="I70" t="n">
+      <c r="J70" t="n">
+        <v>26.5474</v>
+      </c>
+      <c r="K70" t="n">
         <v>0.6637</v>
       </c>
-      <c r="J70" t="n">
+      <c r="L70" t="n">
         <v>3.7538</v>
       </c>
     </row>
@@ -2693,21 +3117,27 @@
         <v>0.9463</v>
       </c>
       <c r="E71" t="n">
+        <v>26.512</v>
+      </c>
+      <c r="F71" t="n">
         <v>0.6627999999999999</v>
       </c>
-      <c r="F71" t="n">
+      <c r="G71" t="n">
         <v>3.7578</v>
       </c>
-      <c r="G71" t="n">
+      <c r="H71" t="n">
         <v>4.3182</v>
       </c>
-      <c r="H71" t="n">
+      <c r="I71" t="n">
         <v>0.8364</v>
       </c>
-      <c r="I71" t="n">
+      <c r="J71" t="n">
+        <v>26.625</v>
+      </c>
+      <c r="K71" t="n">
         <v>0.6656</v>
       </c>
-      <c r="J71" t="n">
+      <c r="L71" t="n">
         <v>3.7549</v>
       </c>
     </row>
@@ -2725,21 +3155,27 @@
         <v>0.9455</v>
       </c>
       <c r="E72" t="n">
+        <v>26.528</v>
+      </c>
+      <c r="F72" t="n">
         <v>0.6632</v>
       </c>
-      <c r="F72" t="n">
+      <c r="G72" t="n">
         <v>3.7563</v>
       </c>
-      <c r="G72" t="n">
+      <c r="H72" t="n">
         <v>4.3205</v>
       </c>
-      <c r="H72" t="n">
+      <c r="I72" t="n">
         <v>0.8383</v>
       </c>
-      <c r="I72" t="n">
+      <c r="J72" t="n">
+        <v>26.6496</v>
+      </c>
+      <c r="K72" t="n">
         <v>0.6662</v>
       </c>
-      <c r="J72" t="n">
+      <c r="L72" t="n">
         <v>3.7546</v>
       </c>
     </row>
@@ -2757,21 +3193,27 @@
         <v>0.9442</v>
       </c>
       <c r="E73" t="n">
+        <v>26.544</v>
+      </c>
+      <c r="F73" t="n">
         <v>0.6636</v>
       </c>
-      <c r="F73" t="n">
+      <c r="G73" t="n">
         <v>3.7573</v>
       </c>
-      <c r="G73" t="n">
+      <c r="H73" t="n">
         <v>4.3218</v>
       </c>
-      <c r="H73" t="n">
+      <c r="I73" t="n">
         <v>0.835</v>
       </c>
-      <c r="I73" t="n">
+      <c r="J73" t="n">
+        <v>26.8235</v>
+      </c>
+      <c r="K73" t="n">
         <v>0.6706</v>
       </c>
-      <c r="J73" t="n">
+      <c r="L73" t="n">
         <v>3.755</v>
       </c>
     </row>
@@ -2789,21 +3231,27 @@
         <v>0.9417</v>
       </c>
       <c r="E74" t="n">
+        <v>26.572</v>
+      </c>
+      <c r="F74" t="n">
         <v>0.6643</v>
       </c>
-      <c r="F74" t="n">
+      <c r="G74" t="n">
         <v>3.7572</v>
       </c>
-      <c r="G74" t="n">
+      <c r="H74" t="n">
         <v>4.3165</v>
       </c>
-      <c r="H74" t="n">
+      <c r="I74" t="n">
         <v>0.8302</v>
       </c>
-      <c r="I74" t="n">
+      <c r="J74" t="n">
+        <v>26.8352</v>
+      </c>
+      <c r="K74" t="n">
         <v>0.6709000000000001</v>
       </c>
-      <c r="J74" t="n">
+      <c r="L74" t="n">
         <v>3.7539</v>
       </c>
     </row>
@@ -2821,21 +3269,27 @@
         <v>0.9405</v>
       </c>
       <c r="E75" t="n">
+        <v>26.576</v>
+      </c>
+      <c r="F75" t="n">
         <v>0.6644</v>
       </c>
-      <c r="F75" t="n">
+      <c r="G75" t="n">
         <v>3.7577</v>
       </c>
-      <c r="G75" t="n">
+      <c r="H75" t="n">
         <v>4.3162</v>
       </c>
-      <c r="H75" t="n">
+      <c r="I75" t="n">
         <v>0.8367</v>
       </c>
-      <c r="I75" t="n">
+      <c r="J75" t="n">
+        <v>26.5554</v>
+      </c>
+      <c r="K75" t="n">
         <v>0.6639</v>
       </c>
-      <c r="J75" t="n">
+      <c r="L75" t="n">
         <v>3.7541</v>
       </c>
     </row>
@@ -2853,21 +3307,27 @@
         <v>0.9381</v>
       </c>
       <c r="E76" t="n">
+        <v>26.596</v>
+      </c>
+      <c r="F76" t="n">
         <v>0.6649</v>
       </c>
-      <c r="F76" t="n">
+      <c r="G76" t="n">
         <v>3.7573</v>
       </c>
-      <c r="G76" t="n">
+      <c r="H76" t="n">
         <v>4.313</v>
       </c>
-      <c r="H76" t="n">
+      <c r="I76" t="n">
         <v>0.8331</v>
       </c>
-      <c r="I76" t="n">
+      <c r="J76" t="n">
+        <v>26.5719</v>
+      </c>
+      <c r="K76" t="n">
         <v>0.6643</v>
       </c>
-      <c r="J76" t="n">
+      <c r="L76" t="n">
         <v>3.7541</v>
       </c>
     </row>
@@ -2885,21 +3345,27 @@
         <v>0.9374</v>
       </c>
       <c r="E77" t="n">
+        <v>26.612</v>
+      </c>
+      <c r="F77" t="n">
         <v>0.6653</v>
       </c>
-      <c r="F77" t="n">
+      <c r="G77" t="n">
         <v>3.7591</v>
       </c>
-      <c r="G77" t="n">
+      <c r="H77" t="n">
         <v>4.3138</v>
       </c>
-      <c r="H77" t="n">
+      <c r="I77" t="n">
         <v>0.8312</v>
       </c>
-      <c r="I77" t="n">
+      <c r="J77" t="n">
+        <v>26.6672</v>
+      </c>
+      <c r="K77" t="n">
         <v>0.6667</v>
       </c>
-      <c r="J77" t="n">
+      <c r="L77" t="n">
         <v>3.7547</v>
       </c>
     </row>
@@ -2917,21 +3383,27 @@
         <v>0.9377</v>
       </c>
       <c r="E78" t="n">
+        <v>26.612</v>
+      </c>
+      <c r="F78" t="n">
         <v>0.6653</v>
       </c>
-      <c r="F78" t="n">
+      <c r="G78" t="n">
         <v>3.757</v>
       </c>
-      <c r="G78" t="n">
+      <c r="H78" t="n">
         <v>4.3126</v>
       </c>
-      <c r="H78" t="n">
+      <c r="I78" t="n">
         <v>0.8331</v>
       </c>
-      <c r="I78" t="n">
+      <c r="J78" t="n">
+        <v>26.579</v>
+      </c>
+      <c r="K78" t="n">
         <v>0.6645</v>
       </c>
-      <c r="J78" t="n">
+      <c r="L78" t="n">
         <v>3.7534</v>
       </c>
     </row>
@@ -2949,21 +3421,27 @@
         <v>0.9360000000000001</v>
       </c>
       <c r="E79" t="n">
+        <v>26.628</v>
+      </c>
+      <c r="F79" t="n">
         <v>0.6657</v>
       </c>
-      <c r="F79" t="n">
+      <c r="G79" t="n">
         <v>3.7566</v>
       </c>
-      <c r="G79" t="n">
+      <c r="H79" t="n">
         <v>4.3136</v>
       </c>
-      <c r="H79" t="n">
+      <c r="I79" t="n">
         <v>0.8371</v>
       </c>
-      <c r="I79" t="n">
+      <c r="J79" t="n">
+        <v>26.4392</v>
+      </c>
+      <c r="K79" t="n">
         <v>0.661</v>
       </c>
-      <c r="J79" t="n">
+      <c r="L79" t="n">
         <v>3.754</v>
       </c>
     </row>
@@ -2981,21 +3459,27 @@
         <v>0.9344</v>
       </c>
       <c r="E80" t="n">
+        <v>26.656</v>
+      </c>
+      <c r="F80" t="n">
         <v>0.6664</v>
       </c>
-      <c r="F80" t="n">
+      <c r="G80" t="n">
         <v>3.7543</v>
       </c>
-      <c r="G80" t="n">
+      <c r="H80" t="n">
         <v>4.3144</v>
       </c>
-      <c r="H80" t="n">
+      <c r="I80" t="n">
         <v>0.831</v>
       </c>
-      <c r="I80" t="n">
+      <c r="J80" t="n">
+        <v>26.7092</v>
+      </c>
+      <c r="K80" t="n">
         <v>0.6677</v>
       </c>
-      <c r="J80" t="n">
+      <c r="L80" t="n">
         <v>3.7541</v>
       </c>
     </row>
@@ -3013,21 +3497,27 @@
         <v>0.9319</v>
       </c>
       <c r="E81" t="n">
+        <v>26.648</v>
+      </c>
+      <c r="F81" t="n">
         <v>0.6662</v>
       </c>
-      <c r="F81" t="n">
+      <c r="G81" t="n">
         <v>3.7562</v>
       </c>
-      <c r="G81" t="n">
+      <c r="H81" t="n">
         <v>4.3104</v>
       </c>
-      <c r="H81" t="n">
+      <c r="I81" t="n">
         <v>0.8276</v>
       </c>
-      <c r="I81" t="n">
+      <c r="J81" t="n">
+        <v>26.6951</v>
+      </c>
+      <c r="K81" t="n">
         <v>0.6674</v>
       </c>
-      <c r="J81" t="n">
+      <c r="L81" t="n">
         <v>3.754</v>
       </c>
     </row>
@@ -3045,21 +3535,27 @@
         <v>0.931</v>
       </c>
       <c r="E82" t="n">
+        <v>26.684</v>
+      </c>
+      <c r="F82" t="n">
         <v>0.6671</v>
       </c>
-      <c r="F82" t="n">
+      <c r="G82" t="n">
         <v>3.7583</v>
       </c>
-      <c r="G82" t="n">
+      <c r="H82" t="n">
         <v>4.3104</v>
       </c>
-      <c r="H82" t="n">
+      <c r="I82" t="n">
         <v>0.8265</v>
       </c>
-      <c r="I82" t="n">
+      <c r="J82" t="n">
+        <v>26.7509</v>
+      </c>
+      <c r="K82" t="n">
         <v>0.6688</v>
       </c>
-      <c r="J82" t="n">
+      <c r="L82" t="n">
         <v>3.7536</v>
       </c>
     </row>
@@ -3077,21 +3573,27 @@
         <v>0.9291</v>
       </c>
       <c r="E83" t="n">
+        <v>26.688</v>
+      </c>
+      <c r="F83" t="n">
         <v>0.6672</v>
       </c>
-      <c r="F83" t="n">
+      <c r="G83" t="n">
         <v>3.758</v>
       </c>
-      <c r="G83" t="n">
+      <c r="H83" t="n">
         <v>4.3111</v>
       </c>
-      <c r="H83" t="n">
+      <c r="I83" t="n">
         <v>0.829</v>
       </c>
-      <c r="I83" t="n">
+      <c r="J83" t="n">
+        <v>26.6721</v>
+      </c>
+      <c r="K83" t="n">
         <v>0.6667999999999999</v>
       </c>
-      <c r="J83" t="n">
+      <c r="L83" t="n">
         <v>3.7537</v>
       </c>
     </row>
@@ -3109,21 +3611,27 @@
         <v>0.9298</v>
       </c>
       <c r="E84" t="n">
+        <v>26.692</v>
+      </c>
+      <c r="F84" t="n">
         <v>0.6673</v>
       </c>
-      <c r="F84" t="n">
+      <c r="G84" t="n">
         <v>3.7573</v>
       </c>
-      <c r="G84" t="n">
+      <c r="H84" t="n">
         <v>4.308</v>
       </c>
-      <c r="H84" t="n">
+      <c r="I84" t="n">
         <v>0.8282</v>
       </c>
-      <c r="I84" t="n">
+      <c r="J84" t="n">
+        <v>26.5869</v>
+      </c>
+      <c r="K84" t="n">
         <v>0.6647</v>
       </c>
-      <c r="J84" t="n">
+      <c r="L84" t="n">
         <v>3.7535</v>
       </c>
     </row>
@@ -3141,21 +3649,27 @@
         <v>0.9272</v>
       </c>
       <c r="E85" t="n">
+        <v>26.72</v>
+      </c>
+      <c r="F85" t="n">
         <v>0.668</v>
       </c>
-      <c r="F85" t="n">
+      <c r="G85" t="n">
         <v>3.7583</v>
       </c>
-      <c r="G85" t="n">
+      <c r="H85" t="n">
         <v>4.3061</v>
       </c>
-      <c r="H85" t="n">
+      <c r="I85" t="n">
         <v>0.8202</v>
       </c>
-      <c r="I85" t="n">
+      <c r="J85" t="n">
+        <v>26.8249</v>
+      </c>
+      <c r="K85" t="n">
         <v>0.6706</v>
       </c>
-      <c r="J85" t="n">
+      <c r="L85" t="n">
         <v>3.7537</v>
       </c>
     </row>
@@ -3173,21 +3687,27 @@
         <v>0.9263</v>
       </c>
       <c r="E86" t="n">
+        <v>26.744</v>
+      </c>
+      <c r="F86" t="n">
         <v>0.6686</v>
       </c>
-      <c r="F86" t="n">
+      <c r="G86" t="n">
         <v>3.7568</v>
       </c>
-      <c r="G86" t="n">
+      <c r="H86" t="n">
         <v>4.3067</v>
       </c>
-      <c r="H86" t="n">
+      <c r="I86" t="n">
         <v>0.8228</v>
       </c>
-      <c r="I86" t="n">
+      <c r="J86" t="n">
+        <v>26.7406</v>
+      </c>
+      <c r="K86" t="n">
         <v>0.6685</v>
       </c>
-      <c r="J86" t="n">
+      <c r="L86" t="n">
         <v>3.7539</v>
       </c>
     </row>
@@ -3205,21 +3725,27 @@
         <v>0.9252</v>
       </c>
       <c r="E87" t="n">
+        <v>26.744</v>
+      </c>
+      <c r="F87" t="n">
         <v>0.6686</v>
       </c>
-      <c r="F87" t="n">
+      <c r="G87" t="n">
         <v>3.756</v>
       </c>
-      <c r="G87" t="n">
+      <c r="H87" t="n">
         <v>4.3075</v>
       </c>
-      <c r="H87" t="n">
+      <c r="I87" t="n">
         <v>0.8207</v>
       </c>
-      <c r="I87" t="n">
+      <c r="J87" t="n">
+        <v>26.8754</v>
+      </c>
+      <c r="K87" t="n">
         <v>0.6719000000000001</v>
       </c>
-      <c r="J87" t="n">
+      <c r="L87" t="n">
         <v>3.7533</v>
       </c>
     </row>
@@ -3237,21 +3763,27 @@
         <v>0.923</v>
       </c>
       <c r="E88" t="n">
+        <v>26.768</v>
+      </c>
+      <c r="F88" t="n">
         <v>0.6692</v>
       </c>
-      <c r="F88" t="n">
+      <c r="G88" t="n">
         <v>3.7543</v>
       </c>
-      <c r="G88" t="n">
+      <c r="H88" t="n">
         <v>4.3116</v>
       </c>
-      <c r="H88" t="n">
+      <c r="I88" t="n">
         <v>0.8214</v>
       </c>
-      <c r="I88" t="n">
+      <c r="J88" t="n">
+        <v>26.9833</v>
+      </c>
+      <c r="K88" t="n">
         <v>0.6746</v>
       </c>
-      <c r="J88" t="n">
+      <c r="L88" t="n">
         <v>3.7541</v>
       </c>
     </row>
@@ -3269,21 +3801,27 @@
         <v>0.9206</v>
       </c>
       <c r="E89" t="n">
+        <v>26.78</v>
+      </c>
+      <c r="F89" t="n">
         <v>0.6695</v>
       </c>
-      <c r="F89" t="n">
+      <c r="G89" t="n">
         <v>3.7542</v>
       </c>
-      <c r="G89" t="n">
+      <c r="H89" t="n">
         <v>4.3017</v>
       </c>
-      <c r="H89" t="n">
+      <c r="I89" t="n">
         <v>0.8182</v>
       </c>
-      <c r="I89" t="n">
+      <c r="J89" t="n">
+        <v>26.7551</v>
+      </c>
+      <c r="K89" t="n">
         <v>0.6689000000000001</v>
       </c>
-      <c r="J89" t="n">
+      <c r="L89" t="n">
         <v>3.7528</v>
       </c>
     </row>
@@ -3301,21 +3839,27 @@
         <v>0.9217</v>
       </c>
       <c r="E90" t="n">
+        <v>26.792</v>
+      </c>
+      <c r="F90" t="n">
         <v>0.6698</v>
       </c>
-      <c r="F90" t="n">
+      <c r="G90" t="n">
         <v>3.7583</v>
       </c>
-      <c r="G90" t="n">
+      <c r="H90" t="n">
         <v>4.3037</v>
       </c>
-      <c r="H90" t="n">
+      <c r="I90" t="n">
         <v>0.8165</v>
       </c>
-      <c r="I90" t="n">
+      <c r="J90" t="n">
+        <v>26.8895</v>
+      </c>
+      <c r="K90" t="n">
         <v>0.6722</v>
       </c>
-      <c r="J90" t="n">
+      <c r="L90" t="n">
         <v>3.7533</v>
       </c>
     </row>
@@ -3333,21 +3877,27 @@
         <v>0.9211</v>
       </c>
       <c r="E91" t="n">
+        <v>26.812</v>
+      </c>
+      <c r="F91" t="n">
         <v>0.6703</v>
       </c>
-      <c r="F91" t="n">
+      <c r="G91" t="n">
         <v>3.7556</v>
       </c>
-      <c r="G91" t="n">
+      <c r="H91" t="n">
         <v>4.3029</v>
       </c>
-      <c r="H91" t="n">
+      <c r="I91" t="n">
         <v>0.8185</v>
       </c>
-      <c r="I91" t="n">
+      <c r="J91" t="n">
+        <v>26.7804</v>
+      </c>
+      <c r="K91" t="n">
         <v>0.6695</v>
       </c>
-      <c r="J91" t="n">
+      <c r="L91" t="n">
         <v>3.7533</v>
       </c>
     </row>
@@ -3365,21 +3915,27 @@
         <v>0.9188</v>
       </c>
       <c r="E92" t="n">
+        <v>26.808</v>
+      </c>
+      <c r="F92" t="n">
         <v>0.6702</v>
       </c>
-      <c r="F92" t="n">
+      <c r="G92" t="n">
         <v>3.7547</v>
       </c>
-      <c r="G92" t="n">
+      <c r="H92" t="n">
         <v>4.3031</v>
       </c>
-      <c r="H92" t="n">
+      <c r="I92" t="n">
         <v>0.8167</v>
       </c>
-      <c r="I92" t="n">
+      <c r="J92" t="n">
+        <v>26.8595</v>
+      </c>
+      <c r="K92" t="n">
         <v>0.6715</v>
       </c>
-      <c r="J92" t="n">
+      <c r="L92" t="n">
         <v>3.7532</v>
       </c>
     </row>
@@ -3397,21 +3953,27 @@
         <v>0.9173</v>
       </c>
       <c r="E93" t="n">
+        <v>26.84</v>
+      </c>
+      <c r="F93" t="n">
         <v>0.671</v>
       </c>
-      <c r="F93" t="n">
+      <c r="G93" t="n">
         <v>3.7566</v>
       </c>
-      <c r="G93" t="n">
+      <c r="H93" t="n">
         <v>4.3024</v>
       </c>
-      <c r="H93" t="n">
+      <c r="I93" t="n">
         <v>0.819</v>
       </c>
-      <c r="I93" t="n">
+      <c r="J93" t="n">
+        <v>26.749</v>
+      </c>
+      <c r="K93" t="n">
         <v>0.6687</v>
       </c>
-      <c r="J93" t="n">
+      <c r="L93" t="n">
         <v>3.7529</v>
       </c>
     </row>
@@ -3429,21 +3991,27 @@
         <v>0.9162</v>
       </c>
       <c r="E94" t="n">
+        <v>26.84</v>
+      </c>
+      <c r="F94" t="n">
         <v>0.671</v>
       </c>
-      <c r="F94" t="n">
+      <c r="G94" t="n">
         <v>3.7577</v>
       </c>
-      <c r="G94" t="n">
+      <c r="H94" t="n">
         <v>4.3023</v>
       </c>
-      <c r="H94" t="n">
+      <c r="I94" t="n">
         <v>0.8139</v>
       </c>
-      <c r="I94" t="n">
+      <c r="J94" t="n">
+        <v>26.969</v>
+      </c>
+      <c r="K94" t="n">
         <v>0.6742</v>
       </c>
-      <c r="J94" t="n">
+      <c r="L94" t="n">
         <v>3.7523</v>
       </c>
     </row>
@@ -3461,21 +4029,27 @@
         <v>0.9156</v>
       </c>
       <c r="E95" t="n">
+        <v>26.844</v>
+      </c>
+      <c r="F95" t="n">
         <v>0.6711</v>
       </c>
-      <c r="F95" t="n">
+      <c r="G95" t="n">
         <v>3.7536</v>
       </c>
-      <c r="G95" t="n">
+      <c r="H95" t="n">
         <v>4.3005</v>
       </c>
-      <c r="H95" t="n">
+      <c r="I95" t="n">
         <v>0.8188</v>
       </c>
-      <c r="I95" t="n">
+      <c r="J95" t="n">
+        <v>26.6995</v>
+      </c>
+      <c r="K95" t="n">
         <v>0.6675</v>
       </c>
-      <c r="J95" t="n">
+      <c r="L95" t="n">
         <v>3.7524</v>
       </c>
     </row>
@@ -3493,21 +4067,27 @@
         <v>0.9127</v>
       </c>
       <c r="E96" t="n">
+        <v>26.868</v>
+      </c>
+      <c r="F96" t="n">
         <v>0.6717</v>
       </c>
-      <c r="F96" t="n">
+      <c r="G96" t="n">
         <v>3.7554</v>
       </c>
-      <c r="G96" t="n">
+      <c r="H96" t="n">
         <v>4.2993</v>
       </c>
-      <c r="H96" t="n">
+      <c r="I96" t="n">
         <v>0.8156</v>
       </c>
-      <c r="I96" t="n">
+      <c r="J96" t="n">
+        <v>26.787</v>
+      </c>
+      <c r="K96" t="n">
         <v>0.6697</v>
       </c>
-      <c r="J96" t="n">
+      <c r="L96" t="n">
         <v>3.752</v>
       </c>
     </row>
@@ -3525,21 +4105,27 @@
         <v>0.9115</v>
       </c>
       <c r="E97" t="n">
+        <v>26.884</v>
+      </c>
+      <c r="F97" t="n">
         <v>0.6721</v>
       </c>
-      <c r="F97" t="n">
+      <c r="G97" t="n">
         <v>3.7602</v>
       </c>
-      <c r="G97" t="n">
+      <c r="H97" t="n">
         <v>4.2985</v>
       </c>
-      <c r="H97" t="n">
+      <c r="I97" t="n">
         <v>0.8109</v>
       </c>
-      <c r="I97" t="n">
+      <c r="J97" t="n">
+        <v>26.9299</v>
+      </c>
+      <c r="K97" t="n">
         <v>0.6732</v>
       </c>
-      <c r="J97" t="n">
+      <c r="L97" t="n">
         <v>3.7524</v>
       </c>
     </row>
@@ -3557,21 +4143,27 @@
         <v>0.9118000000000001</v>
       </c>
       <c r="E98" t="n">
+        <v>26.892</v>
+      </c>
+      <c r="F98" t="n">
         <v>0.6723</v>
       </c>
-      <c r="F98" t="n">
+      <c r="G98" t="n">
         <v>3.7532</v>
       </c>
-      <c r="G98" t="n">
+      <c r="H98" t="n">
         <v>4.298</v>
       </c>
-      <c r="H98" t="n">
+      <c r="I98" t="n">
         <v>0.8101</v>
       </c>
-      <c r="I98" t="n">
+      <c r="J98" t="n">
+        <v>26.9287</v>
+      </c>
+      <c r="K98" t="n">
         <v>0.6732</v>
       </c>
-      <c r="J98" t="n">
+      <c r="L98" t="n">
         <v>3.7529</v>
       </c>
     </row>
@@ -3589,21 +4181,27 @@
         <v>0.9112</v>
       </c>
       <c r="E99" t="n">
+        <v>26.908</v>
+      </c>
+      <c r="F99" t="n">
         <v>0.6727</v>
       </c>
-      <c r="F99" t="n">
+      <c r="G99" t="n">
         <v>3.7552</v>
       </c>
-      <c r="G99" t="n">
+      <c r="H99" t="n">
         <v>4.2971</v>
       </c>
-      <c r="H99" t="n">
+      <c r="I99" t="n">
         <v>0.8088</v>
       </c>
-      <c r="I99" t="n">
+      <c r="J99" t="n">
+        <v>26.9472</v>
+      </c>
+      <c r="K99" t="n">
         <v>0.6737</v>
       </c>
-      <c r="J99" t="n">
+      <c r="L99" t="n">
         <v>3.7529</v>
       </c>
     </row>
@@ -3621,21 +4219,27 @@
         <v>0.9094</v>
       </c>
       <c r="E100" t="n">
+        <v>26.92</v>
+      </c>
+      <c r="F100" t="n">
         <v>0.673</v>
       </c>
-      <c r="F100" t="n">
+      <c r="G100" t="n">
         <v>3.7575</v>
       </c>
-      <c r="G100" t="n">
+      <c r="H100" t="n">
         <v>4.298</v>
       </c>
-      <c r="H100" t="n">
+      <c r="I100" t="n">
         <v>0.8065</v>
       </c>
-      <c r="I100" t="n">
+      <c r="J100" t="n">
+        <v>27.0982</v>
+      </c>
+      <c r="K100" t="n">
         <v>0.6775</v>
       </c>
-      <c r="J100" t="n">
+      <c r="L100" t="n">
         <v>3.752</v>
       </c>
     </row>
@@ -3653,21 +4257,27 @@
         <v>0.9086</v>
       </c>
       <c r="E101" t="n">
+        <v>26.944</v>
+      </c>
+      <c r="F101" t="n">
         <v>0.6736</v>
       </c>
-      <c r="F101" t="n">
+      <c r="G101" t="n">
         <v>3.755</v>
       </c>
-      <c r="G101" t="n">
+      <c r="H101" t="n">
         <v>4.2955</v>
       </c>
-      <c r="H101" t="n">
+      <c r="I101" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="I101" t="n">
+      <c r="J101" t="n">
+        <v>26.8513</v>
+      </c>
+      <c r="K101" t="n">
         <v>0.6713</v>
       </c>
-      <c r="J101" t="n">
+      <c r="L101" t="n">
         <v>3.7522</v>
       </c>
     </row>
@@ -3685,21 +4295,27 @@
         <v>0.9071</v>
       </c>
       <c r="E102" t="n">
+        <v>26.936</v>
+      </c>
+      <c r="F102" t="n">
         <v>0.6734</v>
       </c>
-      <c r="F102" t="n">
+      <c r="G102" t="n">
         <v>3.7545</v>
       </c>
-      <c r="G102" t="n">
+      <c r="H102" t="n">
         <v>4.2944</v>
       </c>
-      <c r="H102" t="n">
+      <c r="I102" t="n">
         <v>0.8002</v>
       </c>
-      <c r="I102" t="n">
+      <c r="J102" t="n">
+        <v>27.1978</v>
+      </c>
+      <c r="K102" t="n">
         <v>0.6798999999999999</v>
       </c>
-      <c r="J102" t="n">
+      <c r="L102" t="n">
         <v>3.7523</v>
       </c>
     </row>
@@ -3717,21 +4333,27 @@
         <v>0.9056</v>
       </c>
       <c r="E103" t="n">
+        <v>26.956</v>
+      </c>
+      <c r="F103" t="n">
         <v>0.6739000000000001</v>
       </c>
-      <c r="F103" t="n">
+      <c r="G103" t="n">
         <v>3.7555</v>
       </c>
-      <c r="G103" t="n">
+      <c r="H103" t="n">
         <v>4.2956</v>
       </c>
-      <c r="H103" t="n">
+      <c r="I103" t="n">
         <v>0.8116</v>
       </c>
-      <c r="I103" t="n">
+      <c r="J103" t="n">
+        <v>26.8161</v>
+      </c>
+      <c r="K103" t="n">
         <v>0.6704</v>
       </c>
-      <c r="J103" t="n">
+      <c r="L103" t="n">
         <v>3.7516</v>
       </c>
     </row>
@@ -3749,21 +4371,27 @@
         <v>0.9046999999999999</v>
       </c>
       <c r="E104" t="n">
+        <v>26.968</v>
+      </c>
+      <c r="F104" t="n">
         <v>0.6742</v>
       </c>
-      <c r="F104" t="n">
+      <c r="G104" t="n">
         <v>3.7583</v>
       </c>
-      <c r="G104" t="n">
+      <c r="H104" t="n">
         <v>4.2958</v>
       </c>
-      <c r="H104" t="n">
+      <c r="I104" t="n">
         <v>0.8076</v>
       </c>
-      <c r="I104" t="n">
+      <c r="J104" t="n">
+        <v>26.949</v>
+      </c>
+      <c r="K104" t="n">
         <v>0.6737</v>
       </c>
-      <c r="J104" t="n">
+      <c r="L104" t="n">
         <v>3.7527</v>
       </c>
     </row>
@@ -3781,21 +4409,27 @@
         <v>0.9026999999999999</v>
       </c>
       <c r="E105" t="n">
+        <v>26.984</v>
+      </c>
+      <c r="F105" t="n">
         <v>0.6746</v>
       </c>
-      <c r="F105" t="n">
+      <c r="G105" t="n">
         <v>3.7536</v>
       </c>
-      <c r="G105" t="n">
+      <c r="H105" t="n">
         <v>4.2954</v>
       </c>
-      <c r="H105" t="n">
+      <c r="I105" t="n">
         <v>0.7999000000000001</v>
       </c>
-      <c r="I105" t="n">
+      <c r="J105" t="n">
+        <v>27.2623</v>
+      </c>
+      <c r="K105" t="n">
         <v>0.6816</v>
       </c>
-      <c r="J105" t="n">
+      <c r="L105" t="n">
         <v>3.7519</v>
       </c>
     </row>
@@ -3813,21 +4447,27 @@
         <v>0.9024</v>
       </c>
       <c r="E106" t="n">
+        <v>26.996</v>
+      </c>
+      <c r="F106" t="n">
         <v>0.6749000000000001</v>
       </c>
-      <c r="F106" t="n">
+      <c r="G106" t="n">
         <v>3.7539</v>
       </c>
-      <c r="G106" t="n">
+      <c r="H106" t="n">
         <v>4.2941</v>
       </c>
-      <c r="H106" t="n">
+      <c r="I106" t="n">
         <v>0.8023</v>
       </c>
-      <c r="I106" t="n">
+      <c r="J106" t="n">
+        <v>27.1024</v>
+      </c>
+      <c r="K106" t="n">
         <v>0.6776</v>
       </c>
-      <c r="J106" t="n">
+      <c r="L106" t="n">
         <v>3.7523</v>
       </c>
     </row>
@@ -3845,21 +4485,27 @@
         <v>0.9008</v>
       </c>
       <c r="E107" t="n">
+        <v>27.024</v>
+      </c>
+      <c r="F107" t="n">
         <v>0.6756</v>
       </c>
-      <c r="F107" t="n">
+      <c r="G107" t="n">
         <v>3.7569</v>
       </c>
-      <c r="G107" t="n">
+      <c r="H107" t="n">
         <v>4.289</v>
       </c>
-      <c r="H107" t="n">
+      <c r="I107" t="n">
         <v>0.7989000000000001</v>
       </c>
-      <c r="I107" t="n">
+      <c r="J107" t="n">
+        <v>27.0339</v>
+      </c>
+      <c r="K107" t="n">
         <v>0.6758</v>
       </c>
-      <c r="J107" t="n">
+      <c r="L107" t="n">
         <v>3.7524</v>
       </c>
     </row>
@@ -3877,21 +4523,27 @@
         <v>0.9003</v>
       </c>
       <c r="E108" t="n">
+        <v>27.024</v>
+      </c>
+      <c r="F108" t="n">
         <v>0.6756</v>
       </c>
-      <c r="F108" t="n">
+      <c r="G108" t="n">
         <v>3.7533</v>
       </c>
-      <c r="G108" t="n">
+      <c r="H108" t="n">
         <v>4.2919</v>
       </c>
-      <c r="H108" t="n">
+      <c r="I108" t="n">
         <v>0.7997</v>
       </c>
-      <c r="I108" t="n">
+      <c r="J108" t="n">
+        <v>27.1485</v>
+      </c>
+      <c r="K108" t="n">
         <v>0.6787</v>
       </c>
-      <c r="J108" t="n">
+      <c r="L108" t="n">
         <v>3.7514</v>
       </c>
     </row>
@@ -3909,21 +4561,27 @@
         <v>0.8991</v>
       </c>
       <c r="E109" t="n">
+        <v>27.032</v>
+      </c>
+      <c r="F109" t="n">
         <v>0.6758</v>
       </c>
-      <c r="F109" t="n">
+      <c r="G109" t="n">
         <v>3.7519</v>
       </c>
-      <c r="G109" t="n">
+      <c r="H109" t="n">
         <v>4.291</v>
       </c>
-      <c r="H109" t="n">
+      <c r="I109" t="n">
         <v>0.8028</v>
       </c>
-      <c r="I109" t="n">
+      <c r="J109" t="n">
+        <v>26.9867</v>
+      </c>
+      <c r="K109" t="n">
         <v>0.6747</v>
       </c>
-      <c r="J109" t="n">
+      <c r="L109" t="n">
         <v>3.7514</v>
       </c>
     </row>
@@ -3941,21 +4599,27 @@
         <v>0.8984</v>
       </c>
       <c r="E110" t="n">
+        <v>27.04</v>
+      </c>
+      <c r="F110" t="n">
         <v>0.676</v>
       </c>
-      <c r="F110" t="n">
+      <c r="G110" t="n">
         <v>3.7553</v>
       </c>
-      <c r="G110" t="n">
+      <c r="H110" t="n">
         <v>4.2897</v>
       </c>
-      <c r="H110" t="n">
+      <c r="I110" t="n">
         <v>0.7995</v>
       </c>
-      <c r="I110" t="n">
+      <c r="J110" t="n">
+        <v>27.0655</v>
+      </c>
+      <c r="K110" t="n">
         <v>0.6766</v>
       </c>
-      <c r="J110" t="n">
+      <c r="L110" t="n">
         <v>3.7514</v>
       </c>
     </row>
@@ -3973,21 +4637,27 @@
         <v>0.8968</v>
       </c>
       <c r="E111" t="n">
+        <v>27.048</v>
+      </c>
+      <c r="F111" t="n">
         <v>0.6762</v>
       </c>
-      <c r="F111" t="n">
+      <c r="G111" t="n">
         <v>3.7542</v>
       </c>
-      <c r="G111" t="n">
+      <c r="H111" t="n">
         <v>4.2898</v>
       </c>
-      <c r="H111" t="n">
+      <c r="I111" t="n">
         <v>0.802</v>
       </c>
-      <c r="I111" t="n">
+      <c r="J111" t="n">
+        <v>26.937</v>
+      </c>
+      <c r="K111" t="n">
         <v>0.6734</v>
       </c>
-      <c r="J111" t="n">
+      <c r="L111" t="n">
         <v>3.7524</v>
       </c>
     </row>
@@ -4005,21 +4675,27 @@
         <v>0.894</v>
       </c>
       <c r="E112" t="n">
+        <v>27.084</v>
+      </c>
+      <c r="F112" t="n">
         <v>0.6771</v>
       </c>
-      <c r="F112" t="n">
+      <c r="G112" t="n">
         <v>3.7573</v>
       </c>
-      <c r="G112" t="n">
+      <c r="H112" t="n">
         <v>4.2895</v>
       </c>
-      <c r="H112" t="n">
+      <c r="I112" t="n">
         <v>0.7958</v>
       </c>
-      <c r="I112" t="n">
+      <c r="J112" t="n">
+        <v>27.1909</v>
+      </c>
+      <c r="K112" t="n">
         <v>0.6798</v>
       </c>
-      <c r="J112" t="n">
+      <c r="L112" t="n">
         <v>3.7519</v>
       </c>
     </row>
@@ -4037,21 +4713,27 @@
         <v>0.8956</v>
       </c>
       <c r="E113" t="n">
+        <v>27.08</v>
+      </c>
+      <c r="F113" t="n">
         <v>0.677</v>
       </c>
-      <c r="F113" t="n">
+      <c r="G113" t="n">
         <v>3.755</v>
       </c>
-      <c r="G113" t="n">
+      <c r="H113" t="n">
         <v>4.2892</v>
       </c>
-      <c r="H113" t="n">
+      <c r="I113" t="n">
         <v>0.7954</v>
       </c>
-      <c r="I113" t="n">
+      <c r="J113" t="n">
+        <v>27.1941</v>
+      </c>
+      <c r="K113" t="n">
         <v>0.6798999999999999</v>
       </c>
-      <c r="J113" t="n">
+      <c r="L113" t="n">
         <v>3.7518</v>
       </c>
     </row>
@@ -4069,21 +4751,27 @@
         <v>0.8954</v>
       </c>
       <c r="E114" t="n">
+        <v>27.104</v>
+      </c>
+      <c r="F114" t="n">
         <v>0.6776</v>
       </c>
-      <c r="F114" t="n">
+      <c r="G114" t="n">
         <v>3.7565</v>
       </c>
-      <c r="G114" t="n">
+      <c r="H114" t="n">
         <v>4.2869</v>
       </c>
-      <c r="H114" t="n">
+      <c r="I114" t="n">
         <v>0.7937</v>
       </c>
-      <c r="I114" t="n">
+      <c r="J114" t="n">
+        <v>27.1702</v>
+      </c>
+      <c r="K114" t="n">
         <v>0.6793</v>
       </c>
-      <c r="J114" t="n">
+      <c r="L114" t="n">
         <v>3.7519</v>
       </c>
     </row>
@@ -4101,21 +4789,27 @@
         <v>0.8932</v>
       </c>
       <c r="E115" t="n">
+        <v>27.108</v>
+      </c>
+      <c r="F115" t="n">
         <v>0.6777</v>
       </c>
-      <c r="F115" t="n">
+      <c r="G115" t="n">
         <v>3.753</v>
       </c>
-      <c r="G115" t="n">
+      <c r="H115" t="n">
         <v>4.2857</v>
       </c>
-      <c r="H115" t="n">
+      <c r="I115" t="n">
         <v>0.7983</v>
       </c>
-      <c r="I115" t="n">
+      <c r="J115" t="n">
+        <v>26.9447</v>
+      </c>
+      <c r="K115" t="n">
         <v>0.6736</v>
       </c>
-      <c r="J115" t="n">
+      <c r="L115" t="n">
         <v>3.7517</v>
       </c>
     </row>
@@ -4133,21 +4827,27 @@
         <v>0.8921</v>
       </c>
       <c r="E116" t="n">
+        <v>27.128</v>
+      </c>
+      <c r="F116" t="n">
         <v>0.6782</v>
       </c>
-      <c r="F116" t="n">
+      <c r="G116" t="n">
         <v>3.7553</v>
       </c>
-      <c r="G116" t="n">
+      <c r="H116" t="n">
         <v>4.2916</v>
       </c>
-      <c r="H116" t="n">
+      <c r="I116" t="n">
         <v>0.7981</v>
       </c>
-      <c r="I116" t="n">
+      <c r="J116" t="n">
+        <v>27.2117</v>
+      </c>
+      <c r="K116" t="n">
         <v>0.6803</v>
       </c>
-      <c r="J116" t="n">
+      <c r="L116" t="n">
         <v>3.751</v>
       </c>
     </row>
@@ -4165,21 +4865,27 @@
         <v>0.8902</v>
       </c>
       <c r="E117" t="n">
+        <v>27.128</v>
+      </c>
+      <c r="F117" t="n">
         <v>0.6782</v>
       </c>
-      <c r="F117" t="n">
+      <c r="G117" t="n">
         <v>3.7536</v>
       </c>
-      <c r="G117" t="n">
+      <c r="H117" t="n">
         <v>4.2853</v>
       </c>
-      <c r="H117" t="n">
+      <c r="I117" t="n">
         <v>0.7921</v>
       </c>
-      <c r="I117" t="n">
+      <c r="J117" t="n">
+        <v>27.1678</v>
+      </c>
+      <c r="K117" t="n">
         <v>0.6792</v>
       </c>
-      <c r="J117" t="n">
+      <c r="L117" t="n">
         <v>3.752</v>
       </c>
     </row>
@@ -4197,21 +4903,27 @@
         <v>0.8888</v>
       </c>
       <c r="E118" t="n">
+        <v>27.144</v>
+      </c>
+      <c r="F118" t="n">
         <v>0.6786</v>
       </c>
-      <c r="F118" t="n">
+      <c r="G118" t="n">
         <v>3.755</v>
       </c>
-      <c r="G118" t="n">
+      <c r="H118" t="n">
         <v>4.2857</v>
       </c>
-      <c r="H118" t="n">
+      <c r="I118" t="n">
         <v>0.7949000000000001</v>
       </c>
-      <c r="I118" t="n">
+      <c r="J118" t="n">
+        <v>27.0945</v>
+      </c>
+      <c r="K118" t="n">
         <v>0.6774</v>
       </c>
-      <c r="J118" t="n">
+      <c r="L118" t="n">
         <v>3.7513</v>
       </c>
     </row>
@@ -4229,21 +4941,27 @@
         <v>0.8901</v>
       </c>
       <c r="E119" t="n">
+        <v>27.156</v>
+      </c>
+      <c r="F119" t="n">
         <v>0.6788999999999999</v>
       </c>
-      <c r="F119" t="n">
+      <c r="G119" t="n">
         <v>3.7541</v>
       </c>
-      <c r="G119" t="n">
+      <c r="H119" t="n">
         <v>4.2867</v>
       </c>
-      <c r="H119" t="n">
+      <c r="I119" t="n">
         <v>0.7943</v>
       </c>
-      <c r="I119" t="n">
+      <c r="J119" t="n">
+        <v>27.1636</v>
+      </c>
+      <c r="K119" t="n">
         <v>0.6791</v>
       </c>
-      <c r="J119" t="n">
+      <c r="L119" t="n">
         <v>3.7511</v>
       </c>
     </row>
@@ -4261,21 +4979,27 @@
         <v>0.8882</v>
       </c>
       <c r="E120" t="n">
+        <v>27.168</v>
+      </c>
+      <c r="F120" t="n">
         <v>0.6792</v>
       </c>
-      <c r="F120" t="n">
+      <c r="G120" t="n">
         <v>3.7554</v>
       </c>
-      <c r="G120" t="n">
+      <c r="H120" t="n">
         <v>4.2842</v>
       </c>
-      <c r="H120" t="n">
+      <c r="I120" t="n">
         <v>0.7865</v>
       </c>
-      <c r="I120" t="n">
+      <c r="J120" t="n">
+        <v>27.3518</v>
+      </c>
+      <c r="K120" t="n">
         <v>0.6838</v>
       </c>
-      <c r="J120" t="n">
+      <c r="L120" t="n">
         <v>3.7519</v>
       </c>
     </row>
@@ -4293,21 +5017,27 @@
         <v>0.8881</v>
       </c>
       <c r="E121" t="n">
+        <v>27.172</v>
+      </c>
+      <c r="F121" t="n">
         <v>0.6793</v>
       </c>
-      <c r="F121" t="n">
+      <c r="G121" t="n">
         <v>3.7561</v>
       </c>
-      <c r="G121" t="n">
+      <c r="H121" t="n">
         <v>4.2831</v>
       </c>
-      <c r="H121" t="n">
+      <c r="I121" t="n">
         <v>0.7877999999999999</v>
       </c>
-      <c r="I121" t="n">
+      <c r="J121" t="n">
+        <v>27.2686</v>
+      </c>
+      <c r="K121" t="n">
         <v>0.6817</v>
       </c>
-      <c r="J121" t="n">
+      <c r="L121" t="n">
         <v>3.7515</v>
       </c>
     </row>
@@ -4325,21 +5055,27 @@
         <v>0.8859</v>
       </c>
       <c r="E122" t="n">
+        <v>27.188</v>
+      </c>
+      <c r="F122" t="n">
         <v>0.6797</v>
       </c>
-      <c r="F122" t="n">
+      <c r="G122" t="n">
         <v>3.7527</v>
       </c>
-      <c r="G122" t="n">
+      <c r="H122" t="n">
         <v>4.283</v>
       </c>
-      <c r="H122" t="n">
+      <c r="I122" t="n">
         <v>0.7894</v>
       </c>
-      <c r="I122" t="n">
+      <c r="J122" t="n">
+        <v>27.2225</v>
+      </c>
+      <c r="K122" t="n">
         <v>0.6806</v>
       </c>
-      <c r="J122" t="n">
+      <c r="L122" t="n">
         <v>3.7508</v>
       </c>
     </row>
@@ -4357,21 +5093,27 @@
         <v>0.8858</v>
       </c>
       <c r="E123" t="n">
+        <v>27.208</v>
+      </c>
+      <c r="F123" t="n">
         <v>0.6802</v>
       </c>
-      <c r="F123" t="n">
+      <c r="G123" t="n">
         <v>3.755</v>
       </c>
-      <c r="G123" t="n">
+      <c r="H123" t="n">
         <v>4.2829</v>
       </c>
-      <c r="H123" t="n">
+      <c r="I123" t="n">
         <v>0.7897</v>
       </c>
-      <c r="I123" t="n">
+      <c r="J123" t="n">
+        <v>27.2037</v>
+      </c>
+      <c r="K123" t="n">
         <v>0.6801</v>
       </c>
-      <c r="J123" t="n">
+      <c r="L123" t="n">
         <v>3.7509</v>
       </c>
     </row>
@@ -4389,21 +5131,27 @@
         <v>0.8841</v>
       </c>
       <c r="E124" t="n">
+        <v>27.228</v>
+      </c>
+      <c r="F124" t="n">
         <v>0.6807</v>
       </c>
-      <c r="F124" t="n">
+      <c r="G124" t="n">
         <v>3.751</v>
       </c>
-      <c r="G124" t="n">
+      <c r="H124" t="n">
         <v>4.281</v>
       </c>
-      <c r="H124" t="n">
+      <c r="I124" t="n">
         <v>0.794</v>
       </c>
-      <c r="I124" t="n">
+      <c r="J124" t="n">
+        <v>26.9428</v>
+      </c>
+      <c r="K124" t="n">
         <v>0.6736</v>
       </c>
-      <c r="J124" t="n">
+      <c r="L124" t="n">
         <v>3.7513</v>
       </c>
     </row>
@@ -4421,21 +5169,27 @@
         <v>0.8819</v>
       </c>
       <c r="E125" t="n">
+        <v>27.224</v>
+      </c>
+      <c r="F125" t="n">
         <v>0.6806</v>
       </c>
-      <c r="F125" t="n">
+      <c r="G125" t="n">
         <v>3.7549</v>
       </c>
-      <c r="G125" t="n">
+      <c r="H125" t="n">
         <v>4.2815</v>
       </c>
-      <c r="H125" t="n">
+      <c r="I125" t="n">
         <v>0.7843</v>
       </c>
-      <c r="I125" t="n">
+      <c r="J125" t="n">
+        <v>27.3363</v>
+      </c>
+      <c r="K125" t="n">
         <v>0.6834</v>
       </c>
-      <c r="J125" t="n">
+      <c r="L125" t="n">
         <v>3.7516</v>
       </c>
     </row>
@@ -4453,21 +5207,27 @@
         <v>0.8818</v>
       </c>
       <c r="E126" t="n">
+        <v>27.244</v>
+      </c>
+      <c r="F126" t="n">
         <v>0.6811</v>
       </c>
-      <c r="F126" t="n">
+      <c r="G126" t="n">
         <v>3.7552</v>
       </c>
-      <c r="G126" t="n">
+      <c r="H126" t="n">
         <v>4.2828</v>
       </c>
-      <c r="H126" t="n">
+      <c r="I126" t="n">
         <v>0.7896</v>
       </c>
-      <c r="I126" t="n">
+      <c r="J126" t="n">
+        <v>27.1768</v>
+      </c>
+      <c r="K126" t="n">
         <v>0.6794</v>
       </c>
-      <c r="J126" t="n">
+      <c r="L126" t="n">
         <v>3.7517</v>
       </c>
     </row>
@@ -4485,21 +5245,27 @@
         <v>0.8819</v>
       </c>
       <c r="E127" t="n">
+        <v>27.252</v>
+      </c>
+      <c r="F127" t="n">
         <v>0.6813</v>
       </c>
-      <c r="F127" t="n">
+      <c r="G127" t="n">
         <v>3.7581</v>
       </c>
-      <c r="G127" t="n">
+      <c r="H127" t="n">
         <v>4.279</v>
       </c>
-      <c r="H127" t="n">
+      <c r="I127" t="n">
         <v>0.7824</v>
       </c>
-      <c r="I127" t="n">
+      <c r="J127" t="n">
+        <v>27.3307</v>
+      </c>
+      <c r="K127" t="n">
         <v>0.6833</v>
       </c>
-      <c r="J127" t="n">
+      <c r="L127" t="n">
         <v>3.7511</v>
       </c>
     </row>
@@ -4517,21 +5283,27 @@
         <v>0.8814</v>
       </c>
       <c r="E128" t="n">
+        <v>27.268</v>
+      </c>
+      <c r="F128" t="n">
         <v>0.6817</v>
       </c>
-      <c r="F128" t="n">
+      <c r="G128" t="n">
         <v>3.7521</v>
       </c>
-      <c r="G128" t="n">
+      <c r="H128" t="n">
         <v>4.2861</v>
       </c>
-      <c r="H128" t="n">
+      <c r="I128" t="n">
         <v>0.7858000000000001</v>
       </c>
-      <c r="I128" t="n">
+      <c r="J128" t="n">
+        <v>27.4942</v>
+      </c>
+      <c r="K128" t="n">
         <v>0.6874</v>
       </c>
-      <c r="J128" t="n">
+      <c r="L128" t="n">
         <v>3.7506</v>
       </c>
     </row>
@@ -4549,21 +5321,27 @@
         <v>0.8786</v>
       </c>
       <c r="E129" t="n">
+        <v>27.284</v>
+      </c>
+      <c r="F129" t="n">
         <v>0.6821</v>
       </c>
-      <c r="F129" t="n">
+      <c r="G129" t="n">
         <v>3.7546</v>
       </c>
-      <c r="G129" t="n">
+      <c r="H129" t="n">
         <v>4.2779</v>
       </c>
-      <c r="H129" t="n">
+      <c r="I129" t="n">
         <v>0.7851</v>
       </c>
-      <c r="I129" t="n">
+      <c r="J129" t="n">
+        <v>27.1846</v>
+      </c>
+      <c r="K129" t="n">
         <v>0.6796</v>
       </c>
-      <c r="J129" t="n">
+      <c r="L129" t="n">
         <v>3.7509</v>
       </c>
     </row>
@@ -4581,21 +5359,27 @@
         <v>0.8784</v>
       </c>
       <c r="E130" t="n">
+        <v>27.284</v>
+      </c>
+      <c r="F130" t="n">
         <v>0.6821</v>
       </c>
-      <c r="F130" t="n">
+      <c r="G130" t="n">
         <v>3.7523</v>
       </c>
-      <c r="G130" t="n">
+      <c r="H130" t="n">
         <v>4.2782</v>
       </c>
-      <c r="H130" t="n">
+      <c r="I130" t="n">
         <v>0.782</v>
       </c>
-      <c r="I130" t="n">
+      <c r="J130" t="n">
+        <v>27.3205</v>
+      </c>
+      <c r="K130" t="n">
         <v>0.6830000000000001</v>
       </c>
-      <c r="J130" t="n">
+      <c r="L130" t="n">
         <v>3.751</v>
       </c>
     </row>
@@ -4613,21 +5397,27 @@
         <v>0.8769</v>
       </c>
       <c r="E131" t="n">
+        <v>27.296</v>
+      </c>
+      <c r="F131" t="n">
         <v>0.6824</v>
       </c>
-      <c r="F131" t="n">
+      <c r="G131" t="n">
         <v>3.7544</v>
       </c>
-      <c r="G131" t="n">
+      <c r="H131" t="n">
         <v>4.2793</v>
       </c>
-      <c r="H131" t="n">
+      <c r="I131" t="n">
         <v>0.7822</v>
       </c>
-      <c r="I131" t="n">
+      <c r="J131" t="n">
+        <v>27.3531</v>
+      </c>
+      <c r="K131" t="n">
         <v>0.6838</v>
       </c>
-      <c r="J131" t="n">
+      <c r="L131" t="n">
         <v>3.7511</v>
       </c>
     </row>
@@ -4645,21 +5435,27 @@
         <v>0.877</v>
       </c>
       <c r="E132" t="n">
+        <v>27.304</v>
+      </c>
+      <c r="F132" t="n">
         <v>0.6826</v>
       </c>
-      <c r="F132" t="n">
+      <c r="G132" t="n">
         <v>3.7541</v>
       </c>
-      <c r="G132" t="n">
+      <c r="H132" t="n">
         <v>4.2788</v>
       </c>
-      <c r="H132" t="n">
+      <c r="I132" t="n">
         <v>0.7774</v>
       </c>
-      <c r="I132" t="n">
+      <c r="J132" t="n">
+        <v>27.5188</v>
+      </c>
+      <c r="K132" t="n">
         <v>0.6879999999999999</v>
       </c>
-      <c r="J132" t="n">
+      <c r="L132" t="n">
         <v>3.7514</v>
       </c>
     </row>
@@ -4677,21 +5473,27 @@
         <v>0.8768</v>
       </c>
       <c r="E133" t="n">
+        <v>27.316</v>
+      </c>
+      <c r="F133" t="n">
         <v>0.6829</v>
       </c>
-      <c r="F133" t="n">
+      <c r="G133" t="n">
         <v>3.7541</v>
       </c>
-      <c r="G133" t="n">
+      <c r="H133" t="n">
         <v>4.2762</v>
       </c>
-      <c r="H133" t="n">
+      <c r="I133" t="n">
         <v>0.7788</v>
       </c>
-      <c r="I133" t="n">
+      <c r="J133" t="n">
+        <v>27.3673</v>
+      </c>
+      <c r="K133" t="n">
         <v>0.6842</v>
       </c>
-      <c r="J133" t="n">
+      <c r="L133" t="n">
         <v>3.751</v>
       </c>
     </row>
@@ -4709,21 +5511,27 @@
         <v>0.8753</v>
       </c>
       <c r="E134" t="n">
+        <v>27.348</v>
+      </c>
+      <c r="F134" t="n">
         <v>0.6837</v>
       </c>
-      <c r="F134" t="n">
+      <c r="G134" t="n">
         <v>3.7542</v>
       </c>
-      <c r="G134" t="n">
+      <c r="H134" t="n">
         <v>4.2754</v>
       </c>
-      <c r="H134" t="n">
+      <c r="I134" t="n">
         <v>0.7819</v>
       </c>
-      <c r="I134" t="n">
+      <c r="J134" t="n">
+        <v>27.2175</v>
+      </c>
+      <c r="K134" t="n">
         <v>0.6804</v>
       </c>
-      <c r="J134" t="n">
+      <c r="L134" t="n">
         <v>3.7508</v>
       </c>
     </row>
@@ -4741,21 +5549,27 @@
         <v>0.8764</v>
       </c>
       <c r="E135" t="n">
+        <v>27.344</v>
+      </c>
+      <c r="F135" t="n">
         <v>0.6836</v>
       </c>
-      <c r="F135" t="n">
+      <c r="G135" t="n">
         <v>3.7541</v>
       </c>
-      <c r="G135" t="n">
+      <c r="H135" t="n">
         <v>4.2777</v>
       </c>
-      <c r="H135" t="n">
+      <c r="I135" t="n">
         <v>0.7832</v>
       </c>
-      <c r="I135" t="n">
+      <c r="J135" t="n">
+        <v>27.2541</v>
+      </c>
+      <c r="K135" t="n">
         <v>0.6814</v>
       </c>
-      <c r="J135" t="n">
+      <c r="L135" t="n">
         <v>3.7508</v>
       </c>
     </row>
@@ -4773,21 +5587,27 @@
         <v>0.8723</v>
       </c>
       <c r="E136" t="n">
+        <v>27.348</v>
+      </c>
+      <c r="F136" t="n">
         <v>0.6837</v>
       </c>
-      <c r="F136" t="n">
+      <c r="G136" t="n">
         <v>3.755</v>
       </c>
-      <c r="G136" t="n">
+      <c r="H136" t="n">
         <v>4.2769</v>
       </c>
-      <c r="H136" t="n">
+      <c r="I136" t="n">
         <v>0.7816</v>
       </c>
-      <c r="I136" t="n">
+      <c r="J136" t="n">
+        <v>27.3109</v>
+      </c>
+      <c r="K136" t="n">
         <v>0.6828</v>
       </c>
-      <c r="J136" t="n">
+      <c r="L136" t="n">
         <v>3.7501</v>
       </c>
     </row>
@@ -4805,21 +5625,27 @@
         <v>0.874</v>
       </c>
       <c r="E137" t="n">
+        <v>27.376</v>
+      </c>
+      <c r="F137" t="n">
         <v>0.6844</v>
       </c>
-      <c r="F137" t="n">
+      <c r="G137" t="n">
         <v>3.7548</v>
       </c>
-      <c r="G137" t="n">
+      <c r="H137" t="n">
         <v>4.2756</v>
       </c>
-      <c r="H137" t="n">
+      <c r="I137" t="n">
         <v>0.7804</v>
       </c>
-      <c r="I137" t="n">
+      <c r="J137" t="n">
+        <v>27.2908</v>
+      </c>
+      <c r="K137" t="n">
         <v>0.6823</v>
       </c>
-      <c r="J137" t="n">
+      <c r="L137" t="n">
         <v>3.7506</v>
       </c>
     </row>
@@ -4837,21 +5663,27 @@
         <v>0.872</v>
       </c>
       <c r="E138" t="n">
+        <v>27.384</v>
+      </c>
+      <c r="F138" t="n">
         <v>0.6846</v>
       </c>
-      <c r="F138" t="n">
+      <c r="G138" t="n">
         <v>3.7532</v>
       </c>
-      <c r="G138" t="n">
+      <c r="H138" t="n">
         <v>4.2745</v>
       </c>
-      <c r="H138" t="n">
+      <c r="I138" t="n">
         <v>0.7805</v>
       </c>
-      <c r="I138" t="n">
+      <c r="J138" t="n">
+        <v>27.2418</v>
+      </c>
+      <c r="K138" t="n">
         <v>0.681</v>
       </c>
-      <c r="J138" t="n">
+      <c r="L138" t="n">
         <v>3.7506</v>
       </c>
     </row>
@@ -4869,21 +5701,27 @@
         <v>0.8713</v>
       </c>
       <c r="E139" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="F139" t="n">
         <v>0.6850000000000001</v>
       </c>
-      <c r="F139" t="n">
+      <c r="G139" t="n">
         <v>3.7513</v>
       </c>
-      <c r="G139" t="n">
+      <c r="H139" t="n">
         <v>4.2725</v>
       </c>
-      <c r="H139" t="n">
+      <c r="I139" t="n">
         <v>0.7761</v>
       </c>
-      <c r="I139" t="n">
+      <c r="J139" t="n">
+        <v>27.3427</v>
+      </c>
+      <c r="K139" t="n">
         <v>0.6836</v>
       </c>
-      <c r="J139" t="n">
+      <c r="L139" t="n">
         <v>3.7504</v>
       </c>
     </row>
@@ -4901,21 +5739,27 @@
         <v>0.8713</v>
       </c>
       <c r="E140" t="n">
+        <v>27.392</v>
+      </c>
+      <c r="F140" t="n">
         <v>0.6848</v>
       </c>
-      <c r="F140" t="n">
+      <c r="G140" t="n">
         <v>3.7567</v>
       </c>
-      <c r="G140" t="n">
+      <c r="H140" t="n">
         <v>4.274</v>
       </c>
-      <c r="H140" t="n">
+      <c r="I140" t="n">
         <v>0.7758</v>
       </c>
-      <c r="I140" t="n">
+      <c r="J140" t="n">
+        <v>27.4235</v>
+      </c>
+      <c r="K140" t="n">
         <v>0.6856</v>
       </c>
-      <c r="J140" t="n">
+      <c r="L140" t="n">
         <v>3.7502</v>
       </c>
     </row>
@@ -4933,21 +5777,27 @@
         <v>0.8702</v>
       </c>
       <c r="E141" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="F141" t="n">
         <v>0.6850000000000001</v>
       </c>
-      <c r="F141" t="n">
+      <c r="G141" t="n">
         <v>3.7524</v>
       </c>
-      <c r="G141" t="n">
+      <c r="H141" t="n">
         <v>4.2731</v>
       </c>
-      <c r="H141" t="n">
+      <c r="I141" t="n">
         <v>0.775</v>
       </c>
-      <c r="I141" t="n">
+      <c r="J141" t="n">
+        <v>27.3987</v>
+      </c>
+      <c r="K141" t="n">
         <v>0.6850000000000001</v>
       </c>
-      <c r="J141" t="n">
+      <c r="L141" t="n">
         <v>3.7508</v>
       </c>
     </row>
@@ -4965,21 +5815,27 @@
         <v>0.8683999999999999</v>
       </c>
       <c r="E142" t="n">
+        <v>27.416</v>
+      </c>
+      <c r="F142" t="n">
         <v>0.6854</v>
       </c>
-      <c r="F142" t="n">
+      <c r="G142" t="n">
         <v>3.752</v>
       </c>
-      <c r="G142" t="n">
+      <c r="H142" t="n">
         <v>4.2734</v>
       </c>
-      <c r="H142" t="n">
+      <c r="I142" t="n">
         <v>0.7776</v>
       </c>
-      <c r="I142" t="n">
+      <c r="J142" t="n">
+        <v>27.3211</v>
+      </c>
+      <c r="K142" t="n">
         <v>0.6830000000000001</v>
       </c>
-      <c r="J142" t="n">
+      <c r="L142" t="n">
         <v>3.7503</v>
       </c>
     </row>
@@ -4997,21 +5853,27 @@
         <v>0.8687</v>
       </c>
       <c r="E143" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="F143" t="n">
         <v>0.6855</v>
       </c>
-      <c r="F143" t="n">
+      <c r="G143" t="n">
         <v>3.7506</v>
       </c>
-      <c r="G143" t="n">
+      <c r="H143" t="n">
         <v>4.2732</v>
       </c>
-      <c r="H143" t="n">
+      <c r="I143" t="n">
         <v>0.7798</v>
       </c>
-      <c r="I143" t="n">
+      <c r="J143" t="n">
+        <v>27.2168</v>
+      </c>
+      <c r="K143" t="n">
         <v>0.6804</v>
       </c>
-      <c r="J143" t="n">
+      <c r="L143" t="n">
         <v>3.7507</v>
       </c>
     </row>
@@ -5029,21 +5891,27 @@
         <v>0.8692</v>
       </c>
       <c r="E144" t="n">
+        <v>27.448</v>
+      </c>
+      <c r="F144" t="n">
         <v>0.6862</v>
       </c>
-      <c r="F144" t="n">
+      <c r="G144" t="n">
         <v>3.7516</v>
       </c>
-      <c r="G144" t="n">
+      <c r="H144" t="n">
         <v>4.2736</v>
       </c>
-      <c r="H144" t="n">
+      <c r="I144" t="n">
         <v>0.7727000000000001</v>
       </c>
-      <c r="I144" t="n">
+      <c r="J144" t="n">
+        <v>27.5189</v>
+      </c>
+      <c r="K144" t="n">
         <v>0.6879999999999999</v>
       </c>
-      <c r="J144" t="n">
+      <c r="L144" t="n">
         <v>3.7506</v>
       </c>
     </row>
@@ -5061,21 +5929,27 @@
         <v>0.8656</v>
       </c>
       <c r="E145" t="n">
+        <v>27.448</v>
+      </c>
+      <c r="F145" t="n">
         <v>0.6862</v>
       </c>
-      <c r="F145" t="n">
+      <c r="G145" t="n">
         <v>3.7534</v>
       </c>
-      <c r="G145" t="n">
+      <c r="H145" t="n">
         <v>4.2708</v>
       </c>
-      <c r="H145" t="n">
+      <c r="I145" t="n">
         <v>0.7671</v>
       </c>
-      <c r="I145" t="n">
+      <c r="J145" t="n">
+        <v>27.6432</v>
+      </c>
+      <c r="K145" t="n">
         <v>0.6911</v>
       </c>
-      <c r="J145" t="n">
+      <c r="L145" t="n">
         <v>3.7501</v>
       </c>
     </row>
@@ -5093,21 +5967,27 @@
         <v>0.8659</v>
       </c>
       <c r="E146" t="n">
+        <v>27.448</v>
+      </c>
+      <c r="F146" t="n">
         <v>0.6862</v>
       </c>
-      <c r="F146" t="n">
+      <c r="G146" t="n">
         <v>3.753</v>
       </c>
-      <c r="G146" t="n">
+      <c r="H146" t="n">
         <v>4.2699</v>
       </c>
-      <c r="H146" t="n">
+      <c r="I146" t="n">
         <v>0.7699</v>
       </c>
-      <c r="I146" t="n">
+      <c r="J146" t="n">
+        <v>27.4778</v>
+      </c>
+      <c r="K146" t="n">
         <v>0.6869</v>
       </c>
-      <c r="J146" t="n">
+      <c r="L146" t="n">
         <v>3.7508</v>
       </c>
     </row>
@@ -5125,21 +6005,27 @@
         <v>0.8653</v>
       </c>
       <c r="E147" t="n">
+        <v>27.468</v>
+      </c>
+      <c r="F147" t="n">
         <v>0.6867</v>
       </c>
-      <c r="F147" t="n">
+      <c r="G147" t="n">
         <v>3.7544</v>
       </c>
-      <c r="G147" t="n">
+      <c r="H147" t="n">
         <v>4.2706</v>
       </c>
-      <c r="H147" t="n">
+      <c r="I147" t="n">
         <v>0.771</v>
       </c>
-      <c r="I147" t="n">
+      <c r="J147" t="n">
+        <v>27.4604</v>
+      </c>
+      <c r="K147" t="n">
         <v>0.6865</v>
       </c>
-      <c r="J147" t="n">
+      <c r="L147" t="n">
         <v>3.7508</v>
       </c>
     </row>
@@ -5157,21 +6043,27 @@
         <v>0.8646</v>
       </c>
       <c r="E148" t="n">
+        <v>27.468</v>
+      </c>
+      <c r="F148" t="n">
         <v>0.6867</v>
       </c>
-      <c r="F148" t="n">
+      <c r="G148" t="n">
         <v>3.7538</v>
       </c>
-      <c r="G148" t="n">
+      <c r="H148" t="n">
         <v>4.2714</v>
       </c>
-      <c r="H148" t="n">
+      <c r="I148" t="n">
         <v>0.7802</v>
       </c>
-      <c r="I148" t="n">
+      <c r="J148" t="n">
+        <v>27.1543</v>
+      </c>
+      <c r="K148" t="n">
         <v>0.6788999999999999</v>
       </c>
-      <c r="J148" t="n">
+      <c r="L148" t="n">
         <v>3.7497</v>
       </c>
     </row>
@@ -5189,21 +6081,27 @@
         <v>0.8649</v>
       </c>
       <c r="E149" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="F149" t="n">
         <v>0.6870000000000001</v>
       </c>
-      <c r="F149" t="n">
+      <c r="G149" t="n">
         <v>3.7542</v>
       </c>
-      <c r="G149" t="n">
+      <c r="H149" t="n">
         <v>4.2709</v>
       </c>
-      <c r="H149" t="n">
+      <c r="I149" t="n">
         <v>0.761</v>
       </c>
-      <c r="I149" t="n">
+      <c r="J149" t="n">
+        <v>27.8892</v>
+      </c>
+      <c r="K149" t="n">
         <v>0.6972</v>
       </c>
-      <c r="J149" t="n">
+      <c r="L149" t="n">
         <v>3.7502</v>
       </c>
     </row>
@@ -5221,21 +6119,27 @@
         <v>0.8631</v>
       </c>
       <c r="E150" t="n">
+        <v>27.484</v>
+      </c>
+      <c r="F150" t="n">
         <v>0.6871</v>
       </c>
-      <c r="F150" t="n">
+      <c r="G150" t="n">
         <v>3.7532</v>
       </c>
-      <c r="G150" t="n">
+      <c r="H150" t="n">
         <v>4.2707</v>
       </c>
-      <c r="H150" t="n">
+      <c r="I150" t="n">
         <v>0.7756999999999999</v>
       </c>
-      <c r="I150" t="n">
+      <c r="J150" t="n">
+        <v>27.2933</v>
+      </c>
+      <c r="K150" t="n">
         <v>0.6823</v>
       </c>
-      <c r="J150" t="n">
+      <c r="L150" t="n">
         <v>3.7502</v>
       </c>
     </row>
@@ -5253,21 +6157,27 @@
         <v>0.8618</v>
       </c>
       <c r="E151" t="n">
+        <v>27.512</v>
+      </c>
+      <c r="F151" t="n">
         <v>0.6878</v>
       </c>
-      <c r="F151" t="n">
+      <c r="G151" t="n">
         <v>3.7511</v>
       </c>
-      <c r="G151" t="n">
+      <c r="H151" t="n">
         <v>4.2699</v>
       </c>
-      <c r="H151" t="n">
+      <c r="I151" t="n">
         <v>0.7743</v>
       </c>
-      <c r="I151" t="n">
+      <c r="J151" t="n">
+        <v>27.3004</v>
+      </c>
+      <c r="K151" t="n">
         <v>0.6825</v>
       </c>
-      <c r="J151" t="n">
+      <c r="L151" t="n">
         <v>3.7508</v>
       </c>
     </row>
@@ -5285,21 +6195,27 @@
         <v>0.8619</v>
       </c>
       <c r="E152" t="n">
+        <v>27.508</v>
+      </c>
+      <c r="F152" t="n">
         <v>0.6877</v>
       </c>
-      <c r="F152" t="n">
+      <c r="G152" t="n">
         <v>3.7555</v>
       </c>
-      <c r="G152" t="n">
+      <c r="H152" t="n">
         <v>4.2706</v>
       </c>
-      <c r="H152" t="n">
+      <c r="I152" t="n">
         <v>0.7701</v>
       </c>
-      <c r="I152" t="n">
+      <c r="J152" t="n">
+        <v>27.5194</v>
+      </c>
+      <c r="K152" t="n">
         <v>0.6879999999999999</v>
       </c>
-      <c r="J152" t="n">
+      <c r="L152" t="n">
         <v>3.7501</v>
       </c>
     </row>
@@ -5317,21 +6233,27 @@
         <v>0.8608</v>
       </c>
       <c r="E153" t="n">
+        <v>27.512</v>
+      </c>
+      <c r="F153" t="n">
         <v>0.6878</v>
       </c>
-      <c r="F153" t="n">
+      <c r="G153" t="n">
         <v>3.7533</v>
       </c>
-      <c r="G153" t="n">
+      <c r="H153" t="n">
         <v>4.2715</v>
       </c>
-      <c r="H153" t="n">
+      <c r="I153" t="n">
         <v>0.7731</v>
       </c>
-      <c r="I153" t="n">
+      <c r="J153" t="n">
+        <v>27.4215</v>
+      </c>
+      <c r="K153" t="n">
         <v>0.6855</v>
       </c>
-      <c r="J153" t="n">
+      <c r="L153" t="n">
         <v>3.7505</v>
       </c>
     </row>
@@ -5349,21 +6271,27 @@
         <v>0.8615</v>
       </c>
       <c r="E154" t="n">
+        <v>27.532</v>
+      </c>
+      <c r="F154" t="n">
         <v>0.6883</v>
       </c>
-      <c r="F154" t="n">
+      <c r="G154" t="n">
         <v>3.7526</v>
       </c>
-      <c r="G154" t="n">
+      <c r="H154" t="n">
         <v>4.2687</v>
       </c>
-      <c r="H154" t="n">
+      <c r="I154" t="n">
         <v>0.7655</v>
       </c>
-      <c r="I154" t="n">
+      <c r="J154" t="n">
+        <v>27.6321</v>
+      </c>
+      <c r="K154" t="n">
         <v>0.6908</v>
       </c>
-      <c r="J154" t="n">
+      <c r="L154" t="n">
         <v>3.7498</v>
       </c>
     </row>
@@ -5381,21 +6309,27 @@
         <v>0.8606</v>
       </c>
       <c r="E155" t="n">
+        <v>27.528</v>
+      </c>
+      <c r="F155" t="n">
         <v>0.6882</v>
       </c>
-      <c r="F155" t="n">
+      <c r="G155" t="n">
         <v>3.7528</v>
       </c>
-      <c r="G155" t="n">
+      <c r="H155" t="n">
         <v>4.2688</v>
       </c>
-      <c r="H155" t="n">
+      <c r="I155" t="n">
         <v>0.7707000000000001</v>
       </c>
-      <c r="I155" t="n">
+      <c r="J155" t="n">
+        <v>27.4416</v>
+      </c>
+      <c r="K155" t="n">
         <v>0.6860000000000001</v>
       </c>
-      <c r="J155" t="n">
+      <c r="L155" t="n">
         <v>3.7494</v>
       </c>
     </row>
@@ -5413,21 +6347,27 @@
         <v>0.8597</v>
       </c>
       <c r="E156" t="n">
+        <v>27.548</v>
+      </c>
+      <c r="F156" t="n">
         <v>0.6887</v>
       </c>
-      <c r="F156" t="n">
+      <c r="G156" t="n">
         <v>3.7534</v>
       </c>
-      <c r="G156" t="n">
+      <c r="H156" t="n">
         <v>4.27</v>
       </c>
-      <c r="H156" t="n">
+      <c r="I156" t="n">
         <v>0.7702</v>
       </c>
-      <c r="I156" t="n">
+      <c r="J156" t="n">
+        <v>27.4972</v>
+      </c>
+      <c r="K156" t="n">
         <v>0.6874</v>
       </c>
-      <c r="J156" t="n">
+      <c r="L156" t="n">
         <v>3.7498</v>
       </c>
     </row>
@@ -5445,21 +6385,27 @@
         <v>0.8588</v>
       </c>
       <c r="E157" t="n">
+        <v>27.548</v>
+      </c>
+      <c r="F157" t="n">
         <v>0.6887</v>
       </c>
-      <c r="F157" t="n">
+      <c r="G157" t="n">
         <v>3.7503</v>
       </c>
-      <c r="G157" t="n">
+      <c r="H157" t="n">
         <v>4.2652</v>
       </c>
-      <c r="H157" t="n">
+      <c r="I157" t="n">
         <v>0.761</v>
       </c>
-      <c r="I157" t="n">
+      <c r="J157" t="n">
+        <v>27.6804</v>
+      </c>
+      <c r="K157" t="n">
         <v>0.6919999999999999</v>
       </c>
-      <c r="J157" t="n">
+      <c r="L157" t="n">
         <v>3.7496</v>
       </c>
     </row>
@@ -5477,21 +6423,27 @@
         <v>0.8589</v>
       </c>
       <c r="E158" t="n">
+        <v>27.576</v>
+      </c>
+      <c r="F158" t="n">
         <v>0.6894</v>
       </c>
-      <c r="F158" t="n">
+      <c r="G158" t="n">
         <v>3.7553</v>
       </c>
-      <c r="G158" t="n">
+      <c r="H158" t="n">
         <v>4.2668</v>
       </c>
-      <c r="H158" t="n">
+      <c r="I158" t="n">
         <v>0.768</v>
       </c>
-      <c r="I158" t="n">
+      <c r="J158" t="n">
+        <v>27.4652</v>
+      </c>
+      <c r="K158" t="n">
         <v>0.6866</v>
       </c>
-      <c r="J158" t="n">
+      <c r="L158" t="n">
         <v>3.7496</v>
       </c>
     </row>
@@ -5509,21 +6461,27 @@
         <v>0.8567</v>
       </c>
       <c r="E159" t="n">
+        <v>27.56</v>
+      </c>
+      <c r="F159" t="n">
         <v>0.6889999999999999</v>
       </c>
-      <c r="F159" t="n">
+      <c r="G159" t="n">
         <v>3.7549</v>
       </c>
-      <c r="G159" t="n">
+      <c r="H159" t="n">
         <v>4.2681</v>
       </c>
-      <c r="H159" t="n">
+      <c r="I159" t="n">
         <v>0.7665</v>
       </c>
-      <c r="I159" t="n">
+      <c r="J159" t="n">
+        <v>27.5786</v>
+      </c>
+      <c r="K159" t="n">
         <v>0.6895</v>
       </c>
-      <c r="J159" t="n">
+      <c r="L159" t="n">
         <v>3.7495</v>
       </c>
     </row>
@@ -5541,21 +6499,27 @@
         <v>0.8563</v>
       </c>
       <c r="E160" t="n">
+        <v>27.58</v>
+      </c>
+      <c r="F160" t="n">
         <v>0.6895</v>
       </c>
-      <c r="F160" t="n">
+      <c r="G160" t="n">
         <v>3.7534</v>
       </c>
-      <c r="G160" t="n">
+      <c r="H160" t="n">
         <v>4.2662</v>
       </c>
-      <c r="H160" t="n">
+      <c r="I160" t="n">
         <v>0.7611</v>
       </c>
-      <c r="I160" t="n">
+      <c r="J160" t="n">
+        <v>27.7071</v>
+      </c>
+      <c r="K160" t="n">
         <v>0.6927</v>
       </c>
-      <c r="J160" t="n">
+      <c r="L160" t="n">
         <v>3.7499</v>
       </c>
     </row>
@@ -5573,21 +6537,27 @@
         <v>0.8562</v>
       </c>
       <c r="E161" t="n">
+        <v>27.584</v>
+      </c>
+      <c r="F161" t="n">
         <v>0.6896</v>
       </c>
-      <c r="F161" t="n">
+      <c r="G161" t="n">
         <v>3.7523</v>
       </c>
-      <c r="G161" t="n">
+      <c r="H161" t="n">
         <v>4.2635</v>
       </c>
-      <c r="H161" t="n">
+      <c r="I161" t="n">
         <v>0.7625</v>
       </c>
-      <c r="I161" t="n">
+      <c r="J161" t="n">
+        <v>27.5441</v>
+      </c>
+      <c r="K161" t="n">
         <v>0.6886</v>
       </c>
-      <c r="J161" t="n">
+      <c r="L161" t="n">
         <v>3.7499</v>
       </c>
     </row>
@@ -5605,21 +6575,27 @@
         <v>0.8557</v>
       </c>
       <c r="E162" t="n">
+        <v>27.592</v>
+      </c>
+      <c r="F162" t="n">
         <v>0.6898</v>
       </c>
-      <c r="F162" t="n">
+      <c r="G162" t="n">
         <v>3.751</v>
       </c>
-      <c r="G162" t="n">
+      <c r="H162" t="n">
         <v>4.2661</v>
       </c>
-      <c r="H162" t="n">
+      <c r="I162" t="n">
         <v>0.7644</v>
       </c>
-      <c r="I162" t="n">
+      <c r="J162" t="n">
+        <v>27.5646</v>
+      </c>
+      <c r="K162" t="n">
         <v>0.6891</v>
       </c>
-      <c r="J162" t="n">
+      <c r="L162" t="n">
         <v>3.7501</v>
       </c>
     </row>
@@ -5637,21 +6613,27 @@
         <v>0.8542999999999999</v>
       </c>
       <c r="E163" t="n">
+        <v>27.612</v>
+      </c>
+      <c r="F163" t="n">
         <v>0.6903</v>
       </c>
-      <c r="F163" t="n">
+      <c r="G163" t="n">
         <v>3.7538</v>
       </c>
-      <c r="G163" t="n">
+      <c r="H163" t="n">
         <v>4.2635</v>
       </c>
-      <c r="H163" t="n">
+      <c r="I163" t="n">
         <v>0.7637</v>
       </c>
-      <c r="I163" t="n">
+      <c r="J163" t="n">
+        <v>27.5131</v>
+      </c>
+      <c r="K163" t="n">
         <v>0.6878</v>
       </c>
-      <c r="J163" t="n">
+      <c r="L163" t="n">
         <v>3.7494</v>
       </c>
     </row>
@@ -5669,21 +6651,27 @@
         <v>0.8546</v>
       </c>
       <c r="E164" t="n">
+        <v>27.596</v>
+      </c>
+      <c r="F164" t="n">
         <v>0.6899</v>
       </c>
-      <c r="F164" t="n">
+      <c r="G164" t="n">
         <v>3.7513</v>
       </c>
-      <c r="G164" t="n">
+      <c r="H164" t="n">
         <v>4.2654</v>
       </c>
-      <c r="H164" t="n">
+      <c r="I164" t="n">
         <v>0.764</v>
       </c>
-      <c r="I164" t="n">
+      <c r="J164" t="n">
+        <v>27.5717</v>
+      </c>
+      <c r="K164" t="n">
         <v>0.6893</v>
       </c>
-      <c r="J164" t="n">
+      <c r="L164" t="n">
         <v>3.7495</v>
       </c>
     </row>
@@ -5701,21 +6689,27 @@
         <v>0.8551</v>
       </c>
       <c r="E165" t="n">
+        <v>27.612</v>
+      </c>
+      <c r="F165" t="n">
         <v>0.6903</v>
       </c>
-      <c r="F165" t="n">
+      <c r="G165" t="n">
         <v>3.7511</v>
       </c>
-      <c r="G165" t="n">
+      <c r="H165" t="n">
         <v>4.2646</v>
       </c>
-      <c r="H165" t="n">
+      <c r="I165" t="n">
         <v>0.7629</v>
       </c>
-      <c r="I165" t="n">
+      <c r="J165" t="n">
+        <v>27.5779</v>
+      </c>
+      <c r="K165" t="n">
         <v>0.6894</v>
       </c>
-      <c r="J165" t="n">
+      <c r="L165" t="n">
         <v>3.7497</v>
       </c>
     </row>
@@ -5733,21 +6727,27 @@
         <v>0.8508</v>
       </c>
       <c r="E166" t="n">
+        <v>27.616</v>
+      </c>
+      <c r="F166" t="n">
         <v>0.6904</v>
       </c>
-      <c r="F166" t="n">
+      <c r="G166" t="n">
         <v>3.7527</v>
       </c>
-      <c r="G166" t="n">
+      <c r="H166" t="n">
         <v>4.2629</v>
       </c>
-      <c r="H166" t="n">
+      <c r="I166" t="n">
         <v>0.7631</v>
       </c>
-      <c r="I166" t="n">
+      <c r="J166" t="n">
+        <v>27.4856</v>
+      </c>
+      <c r="K166" t="n">
         <v>0.6871</v>
       </c>
-      <c r="J166" t="n">
+      <c r="L166" t="n">
         <v>3.7501</v>
       </c>
     </row>
@@ -5765,21 +6765,27 @@
         <v>0.8518</v>
       </c>
       <c r="E167" t="n">
+        <v>27.64</v>
+      </c>
+      <c r="F167" t="n">
         <v>0.6909999999999999</v>
       </c>
-      <c r="F167" t="n">
+      <c r="G167" t="n">
         <v>3.751</v>
       </c>
-      <c r="G167" t="n">
+      <c r="H167" t="n">
         <v>4.2639</v>
       </c>
-      <c r="H167" t="n">
+      <c r="I167" t="n">
         <v>0.7572</v>
       </c>
-      <c r="I167" t="n">
+      <c r="J167" t="n">
+        <v>27.7767</v>
+      </c>
+      <c r="K167" t="n">
         <v>0.6944</v>
       </c>
-      <c r="J167" t="n">
+      <c r="L167" t="n">
         <v>3.7496</v>
       </c>
     </row>
@@ -5797,21 +6803,27 @@
         <v>0.8525</v>
       </c>
       <c r="E168" t="n">
+        <v>27.644</v>
+      </c>
+      <c r="F168" t="n">
         <v>0.6911</v>
       </c>
-      <c r="F168" t="n">
+      <c r="G168" t="n">
         <v>3.7538</v>
       </c>
-      <c r="G168" t="n">
+      <c r="H168" t="n">
         <v>4.2637</v>
       </c>
-      <c r="H168" t="n">
+      <c r="I168" t="n">
         <v>0.7617</v>
       </c>
-      <c r="I168" t="n">
+      <c r="J168" t="n">
+        <v>27.589</v>
+      </c>
+      <c r="K168" t="n">
         <v>0.6897</v>
       </c>
-      <c r="J168" t="n">
+      <c r="L168" t="n">
         <v>3.7498</v>
       </c>
     </row>
@@ -5829,21 +6841,27 @@
         <v>0.8515</v>
       </c>
       <c r="E169" t="n">
+        <v>27.664</v>
+      </c>
+      <c r="F169" t="n">
         <v>0.6916</v>
       </c>
-      <c r="F169" t="n">
+      <c r="G169" t="n">
         <v>3.7524</v>
       </c>
-      <c r="G169" t="n">
+      <c r="H169" t="n">
         <v>4.2628</v>
       </c>
-      <c r="H169" t="n">
+      <c r="I169" t="n">
         <v>0.7593</v>
       </c>
-      <c r="I169" t="n">
+      <c r="J169" t="n">
+        <v>27.6732</v>
+      </c>
+      <c r="K169" t="n">
         <v>0.6918</v>
       </c>
-      <c r="J169" t="n">
+      <c r="L169" t="n">
         <v>3.7489</v>
       </c>
     </row>
@@ -5861,21 +6879,27 @@
         <v>0.8507</v>
       </c>
       <c r="E170" t="n">
+        <v>27.66</v>
+      </c>
+      <c r="F170" t="n">
         <v>0.6915</v>
       </c>
-      <c r="F170" t="n">
+      <c r="G170" t="n">
         <v>3.7543</v>
       </c>
-      <c r="G170" t="n">
+      <c r="H170" t="n">
         <v>4.2631</v>
       </c>
-      <c r="H170" t="n">
+      <c r="I170" t="n">
         <v>0.7613</v>
       </c>
-      <c r="I170" t="n">
+      <c r="J170" t="n">
+        <v>27.5887</v>
+      </c>
+      <c r="K170" t="n">
         <v>0.6897</v>
       </c>
-      <c r="J170" t="n">
+      <c r="L170" t="n">
         <v>3.7494</v>
       </c>
     </row>
@@ -5893,21 +6917,27 @@
         <v>0.8488</v>
       </c>
       <c r="E171" t="n">
+        <v>27.66</v>
+      </c>
+      <c r="F171" t="n">
         <v>0.6915</v>
       </c>
-      <c r="F171" t="n">
+      <c r="G171" t="n">
         <v>3.7519</v>
       </c>
-      <c r="G171" t="n">
+      <c r="H171" t="n">
         <v>4.2604</v>
       </c>
-      <c r="H171" t="n">
+      <c r="I171" t="n">
         <v>0.7523</v>
       </c>
-      <c r="I171" t="n">
+      <c r="J171" t="n">
+        <v>27.8425</v>
+      </c>
+      <c r="K171" t="n">
         <v>0.6961000000000001</v>
       </c>
-      <c r="J171" t="n">
+      <c r="L171" t="n">
         <v>3.7494</v>
       </c>
     </row>
@@ -5925,21 +6955,27 @@
         <v>0.8501</v>
       </c>
       <c r="E172" t="n">
+        <v>27.672</v>
+      </c>
+      <c r="F172" t="n">
         <v>0.6918</v>
       </c>
-      <c r="F172" t="n">
+      <c r="G172" t="n">
         <v>3.7531</v>
       </c>
-      <c r="G172" t="n">
+      <c r="H172" t="n">
         <v>4.2623</v>
       </c>
-      <c r="H172" t="n">
+      <c r="I172" t="n">
         <v>0.7585</v>
       </c>
-      <c r="I172" t="n">
+      <c r="J172" t="n">
+        <v>27.6754</v>
+      </c>
+      <c r="K172" t="n">
         <v>0.6919</v>
       </c>
-      <c r="J172" t="n">
+      <c r="L172" t="n">
         <v>3.7491</v>
       </c>
     </row>
@@ -5957,21 +6993,27 @@
         <v>0.8488</v>
       </c>
       <c r="E173" t="n">
+        <v>27.676</v>
+      </c>
+      <c r="F173" t="n">
         <v>0.6919</v>
       </c>
-      <c r="F173" t="n">
+      <c r="G173" t="n">
         <v>3.7531</v>
       </c>
-      <c r="G173" t="n">
+      <c r="H173" t="n">
         <v>4.2645</v>
       </c>
-      <c r="H173" t="n">
+      <c r="I173" t="n">
         <v>0.7601</v>
       </c>
-      <c r="I173" t="n">
+      <c r="J173" t="n">
+        <v>27.6802</v>
+      </c>
+      <c r="K173" t="n">
         <v>0.6919999999999999</v>
       </c>
-      <c r="J173" t="n">
+      <c r="L173" t="n">
         <v>3.7498</v>
       </c>
     </row>
@@ -5989,21 +7031,27 @@
         <v>0.8486</v>
       </c>
       <c r="E174" t="n">
+        <v>27.68</v>
+      </c>
+      <c r="F174" t="n">
         <v>0.6919999999999999</v>
       </c>
-      <c r="F174" t="n">
+      <c r="G174" t="n">
         <v>3.7521</v>
       </c>
-      <c r="G174" t="n">
+      <c r="H174" t="n">
         <v>4.2623</v>
       </c>
-      <c r="H174" t="n">
+      <c r="I174" t="n">
         <v>0.7576000000000001</v>
       </c>
-      <c r="I174" t="n">
+      <c r="J174" t="n">
+        <v>27.724</v>
+      </c>
+      <c r="K174" t="n">
         <v>0.6931</v>
       </c>
-      <c r="J174" t="n">
+      <c r="L174" t="n">
         <v>3.7488</v>
       </c>
     </row>
@@ -6021,21 +7069,27 @@
         <v>0.848</v>
       </c>
       <c r="E175" t="n">
+        <v>27.692</v>
+      </c>
+      <c r="F175" t="n">
         <v>0.6923</v>
       </c>
-      <c r="F175" t="n">
+      <c r="G175" t="n">
         <v>3.7497</v>
       </c>
-      <c r="G175" t="n">
+      <c r="H175" t="n">
         <v>4.2621</v>
       </c>
-      <c r="H175" t="n">
+      <c r="I175" t="n">
         <v>0.7548</v>
       </c>
-      <c r="I175" t="n">
+      <c r="J175" t="n">
+        <v>27.7976</v>
+      </c>
+      <c r="K175" t="n">
         <v>0.6949</v>
       </c>
-      <c r="J175" t="n">
+      <c r="L175" t="n">
         <v>3.7498</v>
       </c>
     </row>
@@ -6053,21 +7107,27 @@
         <v>0.8476</v>
       </c>
       <c r="E176" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="F176" t="n">
         <v>0.6925</v>
       </c>
-      <c r="F176" t="n">
+      <c r="G176" t="n">
         <v>3.7541</v>
       </c>
-      <c r="G176" t="n">
+      <c r="H176" t="n">
         <v>4.2593</v>
       </c>
-      <c r="H176" t="n">
+      <c r="I176" t="n">
         <v>0.7576000000000001</v>
       </c>
-      <c r="I176" t="n">
+      <c r="J176" t="n">
+        <v>27.5701</v>
+      </c>
+      <c r="K176" t="n">
         <v>0.6893</v>
       </c>
-      <c r="J176" t="n">
+      <c r="L176" t="n">
         <v>3.7499</v>
       </c>
     </row>
@@ -6085,21 +7145,27 @@
         <v>0.8479</v>
       </c>
       <c r="E177" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="F177" t="n">
         <v>0.6925</v>
       </c>
-      <c r="F177" t="n">
+      <c r="G177" t="n">
         <v>3.7516</v>
       </c>
-      <c r="G177" t="n">
+      <c r="H177" t="n">
         <v>4.2591</v>
       </c>
-      <c r="H177" t="n">
+      <c r="I177" t="n">
         <v>0.7547</v>
       </c>
-      <c r="I177" t="n">
+      <c r="J177" t="n">
+        <v>27.6897</v>
+      </c>
+      <c r="K177" t="n">
         <v>0.6922</v>
       </c>
-      <c r="J177" t="n">
+      <c r="L177" t="n">
         <v>3.7496</v>
       </c>
     </row>
@@ -6117,21 +7183,27 @@
         <v>0.8462</v>
       </c>
       <c r="E178" t="n">
+        <v>27.704</v>
+      </c>
+      <c r="F178" t="n">
         <v>0.6926</v>
       </c>
-      <c r="F178" t="n">
+      <c r="G178" t="n">
         <v>3.7523</v>
       </c>
-      <c r="G178" t="n">
+      <c r="H178" t="n">
         <v>4.258</v>
       </c>
-      <c r="H178" t="n">
+      <c r="I178" t="n">
         <v>0.7509</v>
       </c>
-      <c r="I178" t="n">
+      <c r="J178" t="n">
+        <v>27.8037</v>
+      </c>
+      <c r="K178" t="n">
         <v>0.6951000000000001</v>
       </c>
-      <c r="J178" t="n">
+      <c r="L178" t="n">
         <v>3.7494</v>
       </c>
     </row>
@@ -6149,21 +7221,27 @@
         <v>0.8455</v>
       </c>
       <c r="E179" t="n">
+        <v>27.716</v>
+      </c>
+      <c r="F179" t="n">
         <v>0.6929</v>
       </c>
-      <c r="F179" t="n">
+      <c r="G179" t="n">
         <v>3.7526</v>
       </c>
-      <c r="G179" t="n">
+      <c r="H179" t="n">
         <v>4.2627</v>
       </c>
-      <c r="H179" t="n">
+      <c r="I179" t="n">
         <v>0.7582</v>
       </c>
-      <c r="I179" t="n">
+      <c r="J179" t="n">
+        <v>27.6911</v>
+      </c>
+      <c r="K179" t="n">
         <v>0.6923</v>
       </c>
-      <c r="J179" t="n">
+      <c r="L179" t="n">
         <v>3.7496</v>
       </c>
     </row>
@@ -6181,21 +7259,27 @@
         <v>0.8454</v>
       </c>
       <c r="E180" t="n">
+        <v>27.724</v>
+      </c>
+      <c r="F180" t="n">
         <v>0.6931</v>
       </c>
-      <c r="F180" t="n">
+      <c r="G180" t="n">
         <v>3.7528</v>
       </c>
-      <c r="G180" t="n">
+      <c r="H180" t="n">
         <v>4.2592</v>
       </c>
-      <c r="H180" t="n">
+      <c r="I180" t="n">
         <v>0.7518</v>
       </c>
-      <c r="I180" t="n">
+      <c r="J180" t="n">
+        <v>27.8158</v>
+      </c>
+      <c r="K180" t="n">
         <v>0.6954</v>
       </c>
-      <c r="J180" t="n">
+      <c r="L180" t="n">
         <v>3.7493</v>
       </c>
     </row>
@@ -6213,21 +7297,27 @@
         <v>0.8448</v>
       </c>
       <c r="E181" t="n">
+        <v>27.732</v>
+      </c>
+      <c r="F181" t="n">
         <v>0.6933</v>
       </c>
-      <c r="F181" t="n">
+      <c r="G181" t="n">
         <v>3.7514</v>
       </c>
-      <c r="G181" t="n">
+      <c r="H181" t="n">
         <v>4.258</v>
       </c>
-      <c r="H181" t="n">
+      <c r="I181" t="n">
         <v>0.7483</v>
       </c>
-      <c r="I181" t="n">
+      <c r="J181" t="n">
+        <v>27.9102</v>
+      </c>
+      <c r="K181" t="n">
         <v>0.6978</v>
       </c>
-      <c r="J181" t="n">
+      <c r="L181" t="n">
         <v>3.7492</v>
       </c>
     </row>
@@ -6245,21 +7335,27 @@
         <v>0.8448</v>
       </c>
       <c r="E182" t="n">
+        <v>27.732</v>
+      </c>
+      <c r="F182" t="n">
         <v>0.6933</v>
       </c>
-      <c r="F182" t="n">
+      <c r="G182" t="n">
         <v>3.754</v>
       </c>
-      <c r="G182" t="n">
+      <c r="H182" t="n">
         <v>4.2581</v>
       </c>
-      <c r="H182" t="n">
+      <c r="I182" t="n">
         <v>0.7544</v>
       </c>
-      <c r="I182" t="n">
+      <c r="J182" t="n">
+        <v>27.6601</v>
+      </c>
+      <c r="K182" t="n">
         <v>0.6915</v>
       </c>
-      <c r="J182" t="n">
+      <c r="L182" t="n">
         <v>3.7496</v>
       </c>
     </row>
@@ -6277,21 +7373,27 @@
         <v>0.8434</v>
       </c>
       <c r="E183" t="n">
+        <v>27.744</v>
+      </c>
+      <c r="F183" t="n">
         <v>0.6936</v>
       </c>
-      <c r="F183" t="n">
+      <c r="G183" t="n">
         <v>3.7516</v>
       </c>
-      <c r="G183" t="n">
+      <c r="H183" t="n">
         <v>4.2647</v>
       </c>
-      <c r="H183" t="n">
+      <c r="I183" t="n">
         <v>0.7625</v>
       </c>
-      <c r="I183" t="n">
+      <c r="J183" t="n">
+        <v>27.6215</v>
+      </c>
+      <c r="K183" t="n">
         <v>0.6905</v>
       </c>
-      <c r="J183" t="n">
+      <c r="L183" t="n">
         <v>3.7488</v>
       </c>
     </row>
@@ -6309,21 +7411,27 @@
         <v>0.8433</v>
       </c>
       <c r="E184" t="n">
+        <v>27.744</v>
+      </c>
+      <c r="F184" t="n">
         <v>0.6936</v>
       </c>
-      <c r="F184" t="n">
+      <c r="G184" t="n">
         <v>3.7528</v>
       </c>
-      <c r="G184" t="n">
+      <c r="H184" t="n">
         <v>4.2601</v>
       </c>
-      <c r="H184" t="n">
+      <c r="I184" t="n">
         <v>0.7539</v>
       </c>
-      <c r="I184" t="n">
+      <c r="J184" t="n">
+        <v>27.7702</v>
+      </c>
+      <c r="K184" t="n">
         <v>0.6943</v>
       </c>
-      <c r="J184" t="n">
+      <c r="L184" t="n">
         <v>3.7493</v>
       </c>
     </row>
@@ -6341,21 +7449,27 @@
         <v>0.842</v>
       </c>
       <c r="E185" t="n">
+        <v>27.756</v>
+      </c>
+      <c r="F185" t="n">
         <v>0.6939</v>
       </c>
-      <c r="F185" t="n">
+      <c r="G185" t="n">
         <v>3.75</v>
       </c>
-      <c r="G185" t="n">
+      <c r="H185" t="n">
         <v>4.256</v>
       </c>
-      <c r="H185" t="n">
+      <c r="I185" t="n">
         <v>0.7495000000000001</v>
       </c>
-      <c r="I185" t="n">
+      <c r="J185" t="n">
+        <v>27.7942</v>
+      </c>
+      <c r="K185" t="n">
         <v>0.6949</v>
       </c>
-      <c r="J185" t="n">
+      <c r="L185" t="n">
         <v>3.7488</v>
       </c>
     </row>
@@ -6373,21 +7487,27 @@
         <v>0.8433</v>
       </c>
       <c r="E186" t="n">
+        <v>27.76</v>
+      </c>
+      <c r="F186" t="n">
         <v>0.694</v>
       </c>
-      <c r="F186" t="n">
+      <c r="G186" t="n">
         <v>3.7517</v>
       </c>
-      <c r="G186" t="n">
+      <c r="H186" t="n">
         <v>4.2573</v>
       </c>
-      <c r="H186" t="n">
+      <c r="I186" t="n">
         <v>0.7542</v>
       </c>
-      <c r="I186" t="n">
+      <c r="J186" t="n">
+        <v>27.654</v>
+      </c>
+      <c r="K186" t="n">
         <v>0.6913</v>
       </c>
-      <c r="J186" t="n">
+      <c r="L186" t="n">
         <v>3.749</v>
       </c>
     </row>
@@ -6405,21 +7525,27 @@
         <v>0.8418</v>
       </c>
       <c r="E187" t="n">
+        <v>27.764</v>
+      </c>
+      <c r="F187" t="n">
         <v>0.6941000000000001</v>
       </c>
-      <c r="F187" t="n">
+      <c r="G187" t="n">
         <v>3.7519</v>
       </c>
-      <c r="G187" t="n">
+      <c r="H187" t="n">
         <v>4.2572</v>
       </c>
-      <c r="H187" t="n">
+      <c r="I187" t="n">
         <v>0.75</v>
       </c>
-      <c r="I187" t="n">
+      <c r="J187" t="n">
+        <v>27.819</v>
+      </c>
+      <c r="K187" t="n">
         <v>0.6955</v>
       </c>
-      <c r="J187" t="n">
+      <c r="L187" t="n">
         <v>3.7491</v>
       </c>
     </row>
@@ -6437,21 +7563,27 @@
         <v>0.8418</v>
       </c>
       <c r="E188" t="n">
+        <v>27.764</v>
+      </c>
+      <c r="F188" t="n">
         <v>0.6941000000000001</v>
       </c>
-      <c r="F188" t="n">
+      <c r="G188" t="n">
         <v>3.7526</v>
       </c>
-      <c r="G188" t="n">
+      <c r="H188" t="n">
         <v>4.2565</v>
       </c>
-      <c r="H188" t="n">
+      <c r="I188" t="n">
         <v>0.7504999999999999</v>
       </c>
-      <c r="I188" t="n">
+      <c r="J188" t="n">
+        <v>27.7668</v>
+      </c>
+      <c r="K188" t="n">
         <v>0.6942</v>
       </c>
-      <c r="J188" t="n">
+      <c r="L188" t="n">
         <v>3.7491</v>
       </c>
     </row>
@@ -6469,21 +7601,27 @@
         <v>0.841</v>
       </c>
       <c r="E189" t="n">
+        <v>27.776</v>
+      </c>
+      <c r="F189" t="n">
         <v>0.6944</v>
       </c>
-      <c r="F189" t="n">
+      <c r="G189" t="n">
         <v>3.7507</v>
       </c>
-      <c r="G189" t="n">
+      <c r="H189" t="n">
         <v>4.2566</v>
       </c>
-      <c r="H189" t="n">
+      <c r="I189" t="n">
         <v>0.7495000000000001</v>
       </c>
-      <c r="I189" t="n">
+      <c r="J189" t="n">
+        <v>27.7957</v>
+      </c>
+      <c r="K189" t="n">
         <v>0.6949</v>
       </c>
-      <c r="J189" t="n">
+      <c r="L189" t="n">
         <v>3.7497</v>
       </c>
     </row>
@@ -6501,21 +7639,27 @@
         <v>0.8405</v>
       </c>
       <c r="E190" t="n">
+        <v>27.792</v>
+      </c>
+      <c r="F190" t="n">
         <v>0.6948</v>
       </c>
-      <c r="F190" t="n">
+      <c r="G190" t="n">
         <v>3.7506</v>
       </c>
-      <c r="G190" t="n">
+      <c r="H190" t="n">
         <v>4.2598</v>
       </c>
-      <c r="H190" t="n">
+      <c r="I190" t="n">
         <v>0.754</v>
       </c>
-      <c r="I190" t="n">
+      <c r="J190" t="n">
+        <v>27.7706</v>
+      </c>
+      <c r="K190" t="n">
         <v>0.6943</v>
       </c>
-      <c r="J190" t="n">
+      <c r="L190" t="n">
         <v>3.7487</v>
       </c>
     </row>
@@ -6533,21 +7677,27 @@
         <v>0.8403</v>
       </c>
       <c r="E191" t="n">
+        <v>27.788</v>
+      </c>
+      <c r="F191" t="n">
         <v>0.6947</v>
       </c>
-      <c r="F191" t="n">
+      <c r="G191" t="n">
         <v>3.752</v>
       </c>
-      <c r="G191" t="n">
+      <c r="H191" t="n">
         <v>4.2553</v>
       </c>
-      <c r="H191" t="n">
+      <c r="I191" t="n">
         <v>0.7468</v>
       </c>
-      <c r="I191" t="n">
+      <c r="J191" t="n">
+        <v>27.8533</v>
+      </c>
+      <c r="K191" t="n">
         <v>0.6963</v>
       </c>
-      <c r="J191" t="n">
+      <c r="L191" t="n">
         <v>3.7496</v>
       </c>
     </row>
@@ -6565,21 +7715,27 @@
         <v>0.8396</v>
       </c>
       <c r="E192" t="n">
+        <v>27.784</v>
+      </c>
+      <c r="F192" t="n">
         <v>0.6946</v>
       </c>
-      <c r="F192" t="n">
+      <c r="G192" t="n">
         <v>3.7521</v>
       </c>
-      <c r="G192" t="n">
+      <c r="H192" t="n">
         <v>4.2564</v>
       </c>
-      <c r="H192" t="n">
+      <c r="I192" t="n">
         <v>0.7487</v>
       </c>
-      <c r="I192" t="n">
+      <c r="J192" t="n">
+        <v>27.8226</v>
+      </c>
+      <c r="K192" t="n">
         <v>0.6956</v>
       </c>
-      <c r="J192" t="n">
+      <c r="L192" t="n">
         <v>3.7495</v>
       </c>
     </row>
@@ -6597,21 +7753,27 @@
         <v>0.8391999999999999</v>
       </c>
       <c r="E193" t="n">
+        <v>27.788</v>
+      </c>
+      <c r="F193" t="n">
         <v>0.6947</v>
       </c>
-      <c r="F193" t="n">
+      <c r="G193" t="n">
         <v>3.7544</v>
       </c>
-      <c r="G193" t="n">
+      <c r="H193" t="n">
         <v>4.2569</v>
       </c>
-      <c r="H193" t="n">
+      <c r="I193" t="n">
         <v>0.7495000000000001</v>
       </c>
-      <c r="I193" t="n">
+      <c r="J193" t="n">
+        <v>27.8167</v>
+      </c>
+      <c r="K193" t="n">
         <v>0.6954</v>
       </c>
-      <c r="J193" t="n">
+      <c r="L193" t="n">
         <v>3.7493</v>
       </c>
     </row>
@@ -6629,21 +7791,27 @@
         <v>0.8374</v>
       </c>
       <c r="E194" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="F194" t="n">
         <v>0.695</v>
       </c>
-      <c r="F194" t="n">
+      <c r="G194" t="n">
         <v>3.7517</v>
       </c>
-      <c r="G194" t="n">
+      <c r="H194" t="n">
         <v>4.2571</v>
       </c>
-      <c r="H194" t="n">
+      <c r="I194" t="n">
         <v>0.7481</v>
       </c>
-      <c r="I194" t="n">
+      <c r="J194" t="n">
+        <v>27.8944</v>
+      </c>
+      <c r="K194" t="n">
         <v>0.6974</v>
       </c>
-      <c r="J194" t="n">
+      <c r="L194" t="n">
         <v>3.7488</v>
       </c>
     </row>
@@ -6661,21 +7829,27 @@
         <v>0.8381</v>
       </c>
       <c r="E195" t="n">
+        <v>27.804</v>
+      </c>
+      <c r="F195" t="n">
         <v>0.6951000000000001</v>
       </c>
-      <c r="F195" t="n">
+      <c r="G195" t="n">
         <v>3.7516</v>
       </c>
-      <c r="G195" t="n">
+      <c r="H195" t="n">
         <v>4.2548</v>
       </c>
-      <c r="H195" t="n">
+      <c r="I195" t="n">
         <v>0.7467</v>
       </c>
-      <c r="I195" t="n">
+      <c r="J195" t="n">
+        <v>27.8537</v>
+      </c>
+      <c r="K195" t="n">
         <v>0.6963</v>
       </c>
-      <c r="J195" t="n">
+      <c r="L195" t="n">
         <v>3.749</v>
       </c>
     </row>
@@ -6693,21 +7867,27 @@
         <v>0.8385</v>
       </c>
       <c r="E196" t="n">
+        <v>27.804</v>
+      </c>
+      <c r="F196" t="n">
         <v>0.6951000000000001</v>
       </c>
-      <c r="F196" t="n">
+      <c r="G196" t="n">
         <v>3.7507</v>
       </c>
-      <c r="G196" t="n">
+      <c r="H196" t="n">
         <v>4.2547</v>
       </c>
-      <c r="H196" t="n">
+      <c r="I196" t="n">
         <v>0.7406</v>
       </c>
-      <c r="I196" t="n">
+      <c r="J196" t="n">
+        <v>28.0784</v>
+      </c>
+      <c r="K196" t="n">
         <v>0.702</v>
       </c>
-      <c r="J196" t="n">
+      <c r="L196" t="n">
         <v>3.7495</v>
       </c>
     </row>
@@ -6725,21 +7905,27 @@
         <v>0.8386</v>
       </c>
       <c r="E197" t="n">
+        <v>27.808</v>
+      </c>
+      <c r="F197" t="n">
         <v>0.6952</v>
       </c>
-      <c r="F197" t="n">
+      <c r="G197" t="n">
         <v>3.7538</v>
       </c>
-      <c r="G197" t="n">
+      <c r="H197" t="n">
         <v>4.2545</v>
       </c>
-      <c r="H197" t="n">
+      <c r="I197" t="n">
         <v>0.7456</v>
       </c>
-      <c r="I197" t="n">
+      <c r="J197" t="n">
+        <v>27.8813</v>
+      </c>
+      <c r="K197" t="n">
         <v>0.697</v>
       </c>
-      <c r="J197" t="n">
+      <c r="L197" t="n">
         <v>3.7491</v>
       </c>
     </row>
@@ -6757,21 +7943,27 @@
         <v>0.8368</v>
       </c>
       <c r="E198" t="n">
+        <v>27.828</v>
+      </c>
+      <c r="F198" t="n">
         <v>0.6957</v>
       </c>
-      <c r="F198" t="n">
+      <c r="G198" t="n">
         <v>3.7484</v>
       </c>
-      <c r="G198" t="n">
+      <c r="H198" t="n">
         <v>4.2528</v>
       </c>
-      <c r="H198" t="n">
+      <c r="I198" t="n">
         <v>0.7502</v>
       </c>
-      <c r="I198" t="n">
+      <c r="J198" t="n">
+        <v>27.6192</v>
+      </c>
+      <c r="K198" t="n">
         <v>0.6905</v>
       </c>
-      <c r="J198" t="n">
+      <c r="L198" t="n">
         <v>3.7496</v>
       </c>
     </row>
@@ -6789,21 +7981,27 @@
         <v>0.8351</v>
       </c>
       <c r="E199" t="n">
+        <v>27.824</v>
+      </c>
+      <c r="F199" t="n">
         <v>0.6956</v>
       </c>
-      <c r="F199" t="n">
+      <c r="G199" t="n">
         <v>3.7556</v>
       </c>
-      <c r="G199" t="n">
+      <c r="H199" t="n">
         <v>4.2521</v>
       </c>
-      <c r="H199" t="n">
+      <c r="I199" t="n">
         <v>0.7435</v>
       </c>
-      <c r="I199" t="n">
+      <c r="J199" t="n">
+        <v>27.875</v>
+      </c>
+      <c r="K199" t="n">
         <v>0.6969</v>
       </c>
-      <c r="J199" t="n">
+      <c r="L199" t="n">
         <v>3.749</v>
       </c>
     </row>
@@ -6821,21 +8019,27 @@
         <v>0.8361</v>
       </c>
       <c r="E200" t="n">
+        <v>27.848</v>
+      </c>
+      <c r="F200" t="n">
         <v>0.6962</v>
       </c>
-      <c r="F200" t="n">
+      <c r="G200" t="n">
         <v>3.7498</v>
       </c>
-      <c r="G200" t="n">
+      <c r="H200" t="n">
         <v>4.2528</v>
       </c>
-      <c r="H200" t="n">
+      <c r="I200" t="n">
         <v>0.7416</v>
       </c>
-      <c r="I200" t="n">
+      <c r="J200" t="n">
+        <v>27.9713</v>
+      </c>
+      <c r="K200" t="n">
         <v>0.6993</v>
       </c>
-      <c r="J200" t="n">
+      <c r="L200" t="n">
         <v>3.7493</v>
       </c>
     </row>
@@ -6853,21 +8057,27 @@
         <v>0.835</v>
       </c>
       <c r="E201" t="n">
+        <v>27.848</v>
+      </c>
+      <c r="F201" t="n">
         <v>0.6962</v>
       </c>
-      <c r="F201" t="n">
+      <c r="G201" t="n">
         <v>3.7539</v>
       </c>
-      <c r="G201" t="n">
+      <c r="H201" t="n">
         <v>4.2541</v>
       </c>
-      <c r="H201" t="n">
+      <c r="I201" t="n">
         <v>0.744</v>
       </c>
-      <c r="I201" t="n">
+      <c r="J201" t="n">
+        <v>27.9255</v>
+      </c>
+      <c r="K201" t="n">
         <v>0.6981000000000001</v>
       </c>
-      <c r="J201" t="n">
+      <c r="L201" t="n">
         <v>3.7493</v>
       </c>
     </row>
@@ -6885,21 +8095,27 @@
         <v>0.8351</v>
       </c>
       <c r="E202" t="n">
+        <v>27.844</v>
+      </c>
+      <c r="F202" t="n">
         <v>0.6961000000000001</v>
       </c>
-      <c r="F202" t="n">
+      <c r="G202" t="n">
         <v>3.7488</v>
       </c>
-      <c r="G202" t="n">
+      <c r="H202" t="n">
         <v>4.2527</v>
       </c>
-      <c r="H202" t="n">
+      <c r="I202" t="n">
         <v>0.7406</v>
       </c>
-      <c r="I202" t="n">
+      <c r="J202" t="n">
+        <v>28.0037</v>
+      </c>
+      <c r="K202" t="n">
         <v>0.7000999999999999</v>
       </c>
-      <c r="J202" t="n">
+      <c r="L202" t="n">
         <v>3.7493</v>
       </c>
     </row>
@@ -6917,21 +8133,27 @@
         <v>0.8346</v>
       </c>
       <c r="E203" t="n">
+        <v>27.864</v>
+      </c>
+      <c r="F203" t="n">
         <v>0.6966</v>
       </c>
-      <c r="F203" t="n">
+      <c r="G203" t="n">
         <v>3.7502</v>
       </c>
-      <c r="G203" t="n">
+      <c r="H203" t="n">
         <v>4.2571</v>
       </c>
-      <c r="H203" t="n">
+      <c r="I203" t="n">
         <v>0.746</v>
       </c>
-      <c r="I203" t="n">
+      <c r="J203" t="n">
+        <v>27.9766</v>
+      </c>
+      <c r="K203" t="n">
         <v>0.6994</v>
       </c>
-      <c r="J203" t="n">
+      <c r="L203" t="n">
         <v>3.7489</v>
       </c>
     </row>
@@ -6949,21 +8171,27 @@
         <v>0.8337</v>
       </c>
       <c r="E204" t="n">
+        <v>27.848</v>
+      </c>
+      <c r="F204" t="n">
         <v>0.6962</v>
       </c>
-      <c r="F204" t="n">
+      <c r="G204" t="n">
         <v>3.7519</v>
       </c>
-      <c r="G204" t="n">
+      <c r="H204" t="n">
         <v>4.2519</v>
       </c>
-      <c r="H204" t="n">
+      <c r="I204" t="n">
         <v>0.7436</v>
       </c>
-      <c r="I204" t="n">
+      <c r="J204" t="n">
+        <v>27.8682</v>
+      </c>
+      <c r="K204" t="n">
         <v>0.6967</v>
       </c>
-      <c r="J204" t="n">
+      <c r="L204" t="n">
         <v>3.7488</v>
       </c>
     </row>
@@ -6981,21 +8209,27 @@
         <v>0.8332000000000001</v>
       </c>
       <c r="E205" t="n">
+        <v>27.864</v>
+      </c>
+      <c r="F205" t="n">
         <v>0.6966</v>
       </c>
-      <c r="F205" t="n">
+      <c r="G205" t="n">
         <v>3.7509</v>
       </c>
-      <c r="G205" t="n">
+      <c r="H205" t="n">
         <v>4.2531</v>
       </c>
-      <c r="H205" t="n">
+      <c r="I205" t="n">
         <v>0.7441</v>
       </c>
-      <c r="I205" t="n">
+      <c r="J205" t="n">
+        <v>27.8739</v>
+      </c>
+      <c r="K205" t="n">
         <v>0.6968</v>
       </c>
-      <c r="J205" t="n">
+      <c r="L205" t="n">
         <v>3.7495</v>
       </c>
     </row>
@@ -7013,21 +8247,27 @@
         <v>0.8332000000000001</v>
       </c>
       <c r="E206" t="n">
+        <v>27.872</v>
+      </c>
+      <c r="F206" t="n">
         <v>0.6968</v>
       </c>
-      <c r="F206" t="n">
+      <c r="G206" t="n">
         <v>3.7539</v>
       </c>
-      <c r="G206" t="n">
+      <c r="H206" t="n">
         <v>4.2504</v>
       </c>
-      <c r="H206" t="n">
+      <c r="I206" t="n">
         <v>0.7413999999999999</v>
       </c>
-      <c r="I206" t="n">
+      <c r="J206" t="n">
+        <v>27.9061</v>
+      </c>
+      <c r="K206" t="n">
         <v>0.6977</v>
       </c>
-      <c r="J206" t="n">
+      <c r="L206" t="n">
         <v>3.7484</v>
       </c>
     </row>
@@ -7045,21 +8285,27 @@
         <v>0.8337</v>
       </c>
       <c r="E207" t="n">
+        <v>27.872</v>
+      </c>
+      <c r="F207" t="n">
         <v>0.6968</v>
       </c>
-      <c r="F207" t="n">
+      <c r="G207" t="n">
         <v>3.752</v>
       </c>
-      <c r="G207" t="n">
+      <c r="H207" t="n">
         <v>4.2511</v>
       </c>
-      <c r="H207" t="n">
+      <c r="I207" t="n">
         <v>0.7437</v>
       </c>
-      <c r="I207" t="n">
+      <c r="J207" t="n">
+        <v>27.8221</v>
+      </c>
+      <c r="K207" t="n">
         <v>0.6956</v>
       </c>
-      <c r="J207" t="n">
+      <c r="L207" t="n">
         <v>3.7492</v>
       </c>
     </row>
@@ -7077,21 +8323,27 @@
         <v>0.8317</v>
       </c>
       <c r="E208" t="n">
+        <v>27.868</v>
+      </c>
+      <c r="F208" t="n">
         <v>0.6967</v>
       </c>
-      <c r="F208" t="n">
+      <c r="G208" t="n">
         <v>3.7555</v>
       </c>
-      <c r="G208" t="n">
+      <c r="H208" t="n">
         <v>4.252</v>
       </c>
-      <c r="H208" t="n">
+      <c r="I208" t="n">
         <v>0.7474</v>
       </c>
-      <c r="I208" t="n">
+      <c r="J208" t="n">
+        <v>27.7134</v>
+      </c>
+      <c r="K208" t="n">
         <v>0.6928</v>
       </c>
-      <c r="J208" t="n">
+      <c r="L208" t="n">
         <v>3.7489</v>
       </c>
     </row>
@@ -7109,21 +8361,27 @@
         <v>0.8329</v>
       </c>
       <c r="E209" t="n">
+        <v>27.876</v>
+      </c>
+      <c r="F209" t="n">
         <v>0.6969</v>
       </c>
-      <c r="F209" t="n">
+      <c r="G209" t="n">
         <v>3.7517</v>
       </c>
-      <c r="G209" t="n">
+      <c r="H209" t="n">
         <v>4.2513</v>
       </c>
-      <c r="H209" t="n">
+      <c r="I209" t="n">
         <v>0.744</v>
       </c>
-      <c r="I209" t="n">
+      <c r="J209" t="n">
+        <v>27.844</v>
+      </c>
+      <c r="K209" t="n">
         <v>0.6961000000000001</v>
       </c>
-      <c r="J209" t="n">
+      <c r="L209" t="n">
         <v>3.7483</v>
       </c>
     </row>
@@ -7141,21 +8399,27 @@
         <v>0.8317</v>
       </c>
       <c r="E210" t="n">
+        <v>27.896</v>
+      </c>
+      <c r="F210" t="n">
         <v>0.6974</v>
       </c>
-      <c r="F210" t="n">
+      <c r="G210" t="n">
         <v>3.7541</v>
       </c>
-      <c r="G210" t="n">
+      <c r="H210" t="n">
         <v>4.2505</v>
       </c>
-      <c r="H210" t="n">
+      <c r="I210" t="n">
         <v>0.7465000000000001</v>
       </c>
-      <c r="I210" t="n">
+      <c r="J210" t="n">
+        <v>27.6895</v>
+      </c>
+      <c r="K210" t="n">
         <v>0.6922</v>
       </c>
-      <c r="J210" t="n">
+      <c r="L210" t="n">
         <v>3.7491</v>
       </c>
     </row>
@@ -7173,21 +8437,27 @@
         <v>0.831</v>
       </c>
       <c r="E211" t="n">
+        <v>27.896</v>
+      </c>
+      <c r="F211" t="n">
         <v>0.6974</v>
       </c>
-      <c r="F211" t="n">
+      <c r="G211" t="n">
         <v>3.7512</v>
       </c>
-      <c r="G211" t="n">
+      <c r="H211" t="n">
         <v>4.2498</v>
       </c>
-      <c r="H211" t="n">
+      <c r="I211" t="n">
         <v>0.7413999999999999</v>
       </c>
-      <c r="I211" t="n">
+      <c r="J211" t="n">
+        <v>27.8753</v>
+      </c>
+      <c r="K211" t="n">
         <v>0.6969</v>
       </c>
-      <c r="J211" t="n">
+      <c r="L211" t="n">
         <v>3.7487</v>
       </c>
     </row>
@@ -7205,21 +8475,27 @@
         <v>0.8309</v>
       </c>
       <c r="E212" t="n">
+        <v>27.896</v>
+      </c>
+      <c r="F212" t="n">
         <v>0.6974</v>
       </c>
-      <c r="F212" t="n">
+      <c r="G212" t="n">
         <v>3.7518</v>
       </c>
-      <c r="G212" t="n">
+      <c r="H212" t="n">
         <v>4.249</v>
       </c>
-      <c r="H212" t="n">
+      <c r="I212" t="n">
         <v>0.7378</v>
       </c>
-      <c r="I212" t="n">
+      <c r="J212" t="n">
+        <v>27.9782</v>
+      </c>
+      <c r="K212" t="n">
         <v>0.6995</v>
       </c>
-      <c r="J212" t="n">
+      <c r="L212" t="n">
         <v>3.749</v>
       </c>
     </row>
@@ -7237,21 +8513,27 @@
         <v>0.8294</v>
       </c>
       <c r="E213" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="F213" t="n">
         <v>0.6975</v>
       </c>
-      <c r="F213" t="n">
+      <c r="G213" t="n">
         <v>3.7488</v>
       </c>
-      <c r="G213" t="n">
+      <c r="H213" t="n">
         <v>4.2511</v>
       </c>
-      <c r="H213" t="n">
+      <c r="I213" t="n">
         <v>0.7412</v>
       </c>
-      <c r="I213" t="n">
+      <c r="J213" t="n">
+        <v>27.9514</v>
+      </c>
+      <c r="K213" t="n">
         <v>0.6988</v>
       </c>
-      <c r="J213" t="n">
+      <c r="L213" t="n">
         <v>3.7482</v>
       </c>
     </row>
@@ -7269,21 +8551,27 @@
         <v>0.83</v>
       </c>
       <c r="E214" t="n">
+        <v>27.912</v>
+      </c>
+      <c r="F214" t="n">
         <v>0.6978</v>
       </c>
-      <c r="F214" t="n">
+      <c r="G214" t="n">
         <v>3.7513</v>
       </c>
-      <c r="G214" t="n">
+      <c r="H214" t="n">
         <v>4.2503</v>
       </c>
-      <c r="H214" t="n">
+      <c r="I214" t="n">
         <v>0.7349</v>
       </c>
-      <c r="I214" t="n">
+      <c r="J214" t="n">
+        <v>28.1388</v>
+      </c>
+      <c r="K214" t="n">
         <v>0.7035</v>
       </c>
-      <c r="J214" t="n">
+      <c r="L214" t="n">
         <v>3.7492</v>
       </c>
     </row>
@@ -7301,21 +8589,27 @@
         <v>0.8298</v>
       </c>
       <c r="E215" t="n">
+        <v>27.92</v>
+      </c>
+      <c r="F215" t="n">
         <v>0.698</v>
       </c>
-      <c r="F215" t="n">
+      <c r="G215" t="n">
         <v>3.7495</v>
       </c>
-      <c r="G215" t="n">
+      <c r="H215" t="n">
         <v>4.2502</v>
       </c>
-      <c r="H215" t="n">
+      <c r="I215" t="n">
         <v>0.7376</v>
       </c>
-      <c r="I215" t="n">
+      <c r="J215" t="n">
+        <v>28.033</v>
+      </c>
+      <c r="K215" t="n">
         <v>0.7008</v>
       </c>
-      <c r="J215" t="n">
+      <c r="L215" t="n">
         <v>3.7489</v>
       </c>
     </row>
@@ -7333,21 +8627,27 @@
         <v>0.8292</v>
       </c>
       <c r="E216" t="n">
+        <v>27.916</v>
+      </c>
+      <c r="F216" t="n">
         <v>0.6979</v>
       </c>
-      <c r="F216" t="n">
+      <c r="G216" t="n">
         <v>3.7492</v>
       </c>
-      <c r="G216" t="n">
+      <c r="H216" t="n">
         <v>4.2518</v>
       </c>
-      <c r="H216" t="n">
+      <c r="I216" t="n">
         <v>0.7435</v>
       </c>
-      <c r="I216" t="n">
+      <c r="J216" t="n">
+        <v>27.8867</v>
+      </c>
+      <c r="K216" t="n">
         <v>0.6972</v>
       </c>
-      <c r="J216" t="n">
+      <c r="L216" t="n">
         <v>3.7481</v>
       </c>
     </row>
@@ -7365,21 +8665,27 @@
         <v>0.829</v>
       </c>
       <c r="E217" t="n">
+        <v>27.936</v>
+      </c>
+      <c r="F217" t="n">
         <v>0.6984</v>
       </c>
-      <c r="F217" t="n">
+      <c r="G217" t="n">
         <v>3.7517</v>
       </c>
-      <c r="G217" t="n">
+      <c r="H217" t="n">
         <v>4.249</v>
       </c>
-      <c r="H217" t="n">
+      <c r="I217" t="n">
         <v>0.7386</v>
       </c>
-      <c r="I217" t="n">
+      <c r="J217" t="n">
+        <v>27.9556</v>
+      </c>
+      <c r="K217" t="n">
         <v>0.6989</v>
       </c>
-      <c r="J217" t="n">
+      <c r="L217" t="n">
         <v>3.7487</v>
       </c>
     </row>
@@ -7397,21 +8703,27 @@
         <v>0.8279</v>
       </c>
       <c r="E218" t="n">
+        <v>27.928</v>
+      </c>
+      <c r="F218" t="n">
         <v>0.6982</v>
       </c>
-      <c r="F218" t="n">
+      <c r="G218" t="n">
         <v>3.7525</v>
       </c>
-      <c r="G218" t="n">
+      <c r="H218" t="n">
         <v>4.2488</v>
       </c>
-      <c r="H218" t="n">
+      <c r="I218" t="n">
         <v>0.7363</v>
       </c>
-      <c r="I218" t="n">
+      <c r="J218" t="n">
+        <v>28.0432</v>
+      </c>
+      <c r="K218" t="n">
         <v>0.7010999999999999</v>
       </c>
-      <c r="J218" t="n">
+      <c r="L218" t="n">
         <v>3.7485</v>
       </c>
     </row>
@@ -7429,21 +8741,27 @@
         <v>0.8272</v>
       </c>
       <c r="E219" t="n">
+        <v>27.94</v>
+      </c>
+      <c r="F219" t="n">
         <v>0.6985</v>
       </c>
-      <c r="F219" t="n">
+      <c r="G219" t="n">
         <v>3.7511</v>
       </c>
-      <c r="G219" t="n">
+      <c r="H219" t="n">
         <v>4.2469</v>
       </c>
-      <c r="H219" t="n">
+      <c r="I219" t="n">
         <v>0.7365</v>
       </c>
-      <c r="I219" t="n">
+      <c r="J219" t="n">
+        <v>27.9686</v>
+      </c>
+      <c r="K219" t="n">
         <v>0.6992</v>
       </c>
-      <c r="J219" t="n">
+      <c r="L219" t="n">
         <v>3.7482</v>
       </c>
     </row>
@@ -7461,21 +8779,27 @@
         <v>0.829</v>
       </c>
       <c r="E220" t="n">
+        <v>27.944</v>
+      </c>
+      <c r="F220" t="n">
         <v>0.6986</v>
       </c>
-      <c r="F220" t="n">
+      <c r="G220" t="n">
         <v>3.7519</v>
       </c>
-      <c r="G220" t="n">
+      <c r="H220" t="n">
         <v>4.2486</v>
       </c>
-      <c r="H220" t="n">
+      <c r="I220" t="n">
         <v>0.7426</v>
       </c>
-      <c r="I220" t="n">
+      <c r="J220" t="n">
+        <v>27.7697</v>
+      </c>
+      <c r="K220" t="n">
         <v>0.6942</v>
       </c>
-      <c r="J220" t="n">
+      <c r="L220" t="n">
         <v>3.749</v>
       </c>
     </row>
@@ -7493,21 +8817,27 @@
         <v>0.8272</v>
       </c>
       <c r="E221" t="n">
+        <v>27.928</v>
+      </c>
+      <c r="F221" t="n">
         <v>0.6982</v>
       </c>
-      <c r="F221" t="n">
+      <c r="G221" t="n">
         <v>3.7522</v>
       </c>
-      <c r="G221" t="n">
+      <c r="H221" t="n">
         <v>4.248</v>
       </c>
-      <c r="H221" t="n">
+      <c r="I221" t="n">
         <v>0.7376</v>
       </c>
-      <c r="I221" t="n">
+      <c r="J221" t="n">
+        <v>27.9492</v>
+      </c>
+      <c r="K221" t="n">
         <v>0.6987</v>
       </c>
-      <c r="J221" t="n">
+      <c r="L221" t="n">
         <v>3.7488</v>
       </c>
     </row>
@@ -7525,21 +8855,27 @@
         <v>0.8262</v>
       </c>
       <c r="E222" t="n">
+        <v>27.948</v>
+      </c>
+      <c r="F222" t="n">
         <v>0.6987</v>
       </c>
-      <c r="F222" t="n">
+      <c r="G222" t="n">
         <v>3.7508</v>
       </c>
-      <c r="G222" t="n">
+      <c r="H222" t="n">
         <v>4.2479</v>
       </c>
-      <c r="H222" t="n">
+      <c r="I222" t="n">
         <v>0.7363</v>
       </c>
-      <c r="I222" t="n">
+      <c r="J222" t="n">
+        <v>28.0027</v>
+      </c>
+      <c r="K222" t="n">
         <v>0.7000999999999999</v>
       </c>
-      <c r="J222" t="n">
+      <c r="L222" t="n">
         <v>3.7487</v>
       </c>
     </row>
@@ -7557,21 +8893,27 @@
         <v>0.8274</v>
       </c>
       <c r="E223" t="n">
+        <v>27.964</v>
+      </c>
+      <c r="F223" t="n">
         <v>0.6991000000000001</v>
       </c>
-      <c r="F223" t="n">
+      <c r="G223" t="n">
         <v>3.7521</v>
       </c>
-      <c r="G223" t="n">
+      <c r="H223" t="n">
         <v>4.2526</v>
       </c>
-      <c r="H223" t="n">
+      <c r="I223" t="n">
         <v>0.7386</v>
       </c>
-      <c r="I223" t="n">
+      <c r="J223" t="n">
+        <v>28.0869</v>
+      </c>
+      <c r="K223" t="n">
         <v>0.7022</v>
       </c>
-      <c r="J223" t="n">
+      <c r="L223" t="n">
         <v>3.7491</v>
       </c>
     </row>
@@ -7589,21 +8931,27 @@
         <v>0.8305</v>
       </c>
       <c r="E224" t="n">
+        <v>27.976</v>
+      </c>
+      <c r="F224" t="n">
         <v>0.6994</v>
       </c>
-      <c r="F224" t="n">
+      <c r="G224" t="n">
         <v>3.7527</v>
       </c>
-      <c r="G224" t="n">
+      <c r="H224" t="n">
         <v>4.2502</v>
       </c>
-      <c r="H224" t="n">
+      <c r="I224" t="n">
         <v>0.7412</v>
       </c>
-      <c r="I224" t="n">
+      <c r="J224" t="n">
+        <v>27.8944</v>
+      </c>
+      <c r="K224" t="n">
         <v>0.6974</v>
       </c>
-      <c r="J224" t="n">
+      <c r="L224" t="n">
         <v>3.7488</v>
       </c>
     </row>
@@ -7621,21 +8969,27 @@
         <v>0.8297</v>
       </c>
       <c r="E225" t="n">
+        <v>27.98</v>
+      </c>
+      <c r="F225" t="n">
         <v>0.6995</v>
       </c>
-      <c r="F225" t="n">
+      <c r="G225" t="n">
         <v>3.7473</v>
       </c>
-      <c r="G225" t="n">
+      <c r="H225" t="n">
         <v>4.2504</v>
       </c>
-      <c r="H225" t="n">
+      <c r="I225" t="n">
         <v>0.7385</v>
       </c>
-      <c r="I225" t="n">
+      <c r="J225" t="n">
+        <v>28.03</v>
+      </c>
+      <c r="K225" t="n">
         <v>0.7007</v>
       </c>
-      <c r="J225" t="n">
+      <c r="L225" t="n">
         <v>3.7481</v>
       </c>
     </row>
@@ -7653,21 +9007,27 @@
         <v>0.828</v>
       </c>
       <c r="E226" t="n">
+        <v>27.968</v>
+      </c>
+      <c r="F226" t="n">
         <v>0.6992</v>
       </c>
-      <c r="F226" t="n">
+      <c r="G226" t="n">
         <v>3.751</v>
       </c>
-      <c r="G226" t="n">
+      <c r="H226" t="n">
         <v>4.2486</v>
       </c>
-      <c r="H226" t="n">
+      <c r="I226" t="n">
         <v>0.7364000000000001</v>
       </c>
-      <c r="I226" t="n">
+      <c r="J226" t="n">
+        <v>28.0315</v>
+      </c>
+      <c r="K226" t="n">
         <v>0.7008</v>
       </c>
-      <c r="J226" t="n">
+      <c r="L226" t="n">
         <v>3.7485</v>
       </c>
     </row>
@@ -7685,21 +9045,27 @@
         <v>0.8267</v>
       </c>
       <c r="E227" t="n">
+        <v>27.968</v>
+      </c>
+      <c r="F227" t="n">
         <v>0.6992</v>
       </c>
-      <c r="F227" t="n">
+      <c r="G227" t="n">
         <v>3.7507</v>
       </c>
-      <c r="G227" t="n">
+      <c r="H227" t="n">
         <v>4.2524</v>
       </c>
-      <c r="H227" t="n">
+      <c r="I227" t="n">
         <v>0.7427</v>
       </c>
-      <c r="I227" t="n">
+      <c r="J227" t="n">
+        <v>27.9541</v>
+      </c>
+      <c r="K227" t="n">
         <v>0.6989</v>
       </c>
-      <c r="J227" t="n">
+      <c r="L227" t="n">
         <v>3.7478</v>
       </c>
     </row>
@@ -7717,21 +9083,27 @@
         <v>0.8268</v>
       </c>
       <c r="E228" t="n">
+        <v>27.976</v>
+      </c>
+      <c r="F228" t="n">
         <v>0.6994</v>
       </c>
-      <c r="F228" t="n">
+      <c r="G228" t="n">
         <v>3.7543</v>
       </c>
-      <c r="G228" t="n">
+      <c r="H228" t="n">
         <v>4.248</v>
       </c>
-      <c r="H228" t="n">
+      <c r="I228" t="n">
         <v>0.7375</v>
       </c>
-      <c r="I228" t="n">
+      <c r="J228" t="n">
+        <v>27.9616</v>
+      </c>
+      <c r="K228" t="n">
         <v>0.699</v>
       </c>
-      <c r="J228" t="n">
+      <c r="L228" t="n">
         <v>3.7486</v>
       </c>
     </row>
